--- a/ROSA_vitaSPEC/Results/test_pretraitements/total.carotenes/Resultats_total.carotenes_moy_ADJR2.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/total.carotenes/Resultats_total.carotenes_moy_ADJR2.xlsx
@@ -1,21 +1,217 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\total.carotenes\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+  <si>
+    <t>Pretraitement</t>
+  </si>
+  <si>
+    <t>LV1_ADJR2</t>
+  </si>
+  <si>
+    <t>LV2_ADJR2</t>
+  </si>
+  <si>
+    <t>LV3_ADJR2</t>
+  </si>
+  <si>
+    <t>LV4_ADJR2</t>
+  </si>
+  <si>
+    <t>LV5_ADJR2</t>
+  </si>
+  <si>
+    <t>LV6_ADJR2</t>
+  </si>
+  <si>
+    <t>LV7_ADJR2</t>
+  </si>
+  <si>
+    <t>LV8_ADJR2</t>
+  </si>
+  <si>
+    <t>LV9_ADJR2</t>
+  </si>
+  <si>
+    <t>LV10_ADJR2</t>
+  </si>
+  <si>
+    <t>LV11_ADJR2</t>
+  </si>
+  <si>
+    <t>LV12_ADJR2</t>
+  </si>
+  <si>
+    <t>LV13_ADJR2</t>
+  </si>
+  <si>
+    <t>LV14_ADJR2</t>
+  </si>
+  <si>
+    <t>LV15_ADJR2</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1000,1)_snv_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_msc_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_snv_sder_c(1,3,5)_</t>
+  </si>
+  <si>
+    <t>adj_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -61,13 +257,40 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF9C0006"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF9C0006"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF9C0006"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF9C0006"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -109,7 +332,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -141,9 +364,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -175,6 +399,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -350,305 +575,268 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P47"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="52.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="16" width="14" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Pretraitement</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>LV1_ADJR2</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>LV2_ADJR2</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>LV3_ADJR2</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>LV4_ADJR2</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>LV5_ADJR2</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>LV6_ADJR2</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>LV7_ADJR2</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>LV8_ADJR2</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>LV9_ADJR2</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>LV10_ADJR2</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>LV11_ADJR2</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>LV12_ADJR2</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>LV13_ADJR2</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>LV14_ADJR2</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>LV15_ADJR2</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1000,1)_snv_</t>
-        </is>
+    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>16</v>
       </c>
       <c r="B2">
-        <v>0.3614436311896939</v>
+        <v>0.36144363118969391</v>
       </c>
       <c r="C2">
-        <v>0.5313316659605551</v>
+        <v>0.53133166596055514</v>
       </c>
       <c r="D2">
-        <v>0.5685761211640061</v>
+        <v>0.56857612116400613</v>
       </c>
       <c r="E2">
-        <v>0.6090760569142791</v>
+        <v>0.60907605691427913</v>
       </c>
       <c r="F2">
-        <v>0.6222948668852277</v>
+        <v>0.62229486688522773</v>
       </c>
       <c r="G2">
-        <v>0.6433452467638295</v>
+        <v>0.64334524676382954</v>
       </c>
       <c r="H2">
         <v>0.6506065391814585</v>
       </c>
       <c r="I2">
-        <v>0.6403174525785214</v>
+        <v>0.64031745257852135</v>
       </c>
       <c r="J2">
-        <v>0.6262073696686533</v>
+        <v>0.62620736966865331</v>
       </c>
       <c r="K2">
-        <v>0.6078334265646144</v>
+        <v>0.60783342656461437</v>
       </c>
       <c r="L2">
-        <v>0.6036890782593928</v>
+        <v>0.60368907825939278</v>
       </c>
       <c r="M2">
-        <v>0.5669017433555826</v>
+        <v>0.56690174335558263</v>
       </c>
       <c r="N2">
-        <v>0.5321628854478262</v>
+        <v>0.53216288544782619</v>
       </c>
       <c r="O2">
-        <v>0.5182504704247515</v>
+        <v>0.51825047042475147</v>
       </c>
       <c r="P2">
-        <v>0.5400944466119728</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.54009444661197281</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>17</v>
       </c>
       <c r="B3">
-        <v>0.4407895866316051</v>
+        <v>0.44078958663160511</v>
       </c>
       <c r="C3">
-        <v>0.5471341836549105</v>
+        <v>0.54713418365491051</v>
       </c>
       <c r="D3">
         <v>0.5497565610723455</v>
       </c>
       <c r="E3">
-        <v>0.5563198298318658</v>
+        <v>0.55631982983186579</v>
       </c>
       <c r="F3">
         <v>0.5425640380366944</v>
       </c>
       <c r="G3">
-        <v>0.5382900806800351</v>
+        <v>0.53829008068003514</v>
       </c>
       <c r="H3">
-        <v>0.494283701994245</v>
+        <v>0.49428370199424498</v>
       </c>
       <c r="I3">
-        <v>0.4827155837112919</v>
+        <v>0.48271558371129192</v>
       </c>
       <c r="J3">
-        <v>0.4674295862092707</v>
+        <v>0.46742958620927072</v>
       </c>
       <c r="K3">
         <v>0.4737545515285877</v>
       </c>
       <c r="L3">
-        <v>0.4531091461585469</v>
+        <v>0.45310914615854692</v>
       </c>
       <c r="M3">
-        <v>0.3948830203957919</v>
+        <v>0.39488302039579187</v>
       </c>
       <c r="N3">
-        <v>0.3318376883502631</v>
+        <v>0.33183768835026312</v>
       </c>
       <c r="O3">
-        <v>0.2875808658030823</v>
+        <v>0.28758086580308229</v>
       </c>
       <c r="P3">
-        <v>0.2436385005875827</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_msc_</t>
-        </is>
+        <v>0.24363850058758271</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>18</v>
       </c>
       <c r="B4">
-        <v>0.383077531199022</v>
+        <v>0.38307753119902199</v>
       </c>
       <c r="C4">
-        <v>0.5160776315605207</v>
+        <v>0.51607763156052067</v>
       </c>
       <c r="D4">
-        <v>0.5307688666588882</v>
+        <v>0.53076886665888823</v>
       </c>
       <c r="E4">
-        <v>0.5316256526473221</v>
+        <v>0.53162565264732209</v>
       </c>
       <c r="F4">
-        <v>0.5463439892445631</v>
+        <v>0.54634398924456307</v>
       </c>
       <c r="G4">
-        <v>0.5771384736911225</v>
+        <v>0.57713847369112248</v>
       </c>
       <c r="H4">
-        <v>0.6031742160559749</v>
+        <v>0.60317421605597488</v>
       </c>
       <c r="I4">
-        <v>0.5773041947291843</v>
+        <v>0.57730419472918426</v>
       </c>
       <c r="J4">
-        <v>0.5610402283885831</v>
+        <v>0.56104022838858314</v>
       </c>
       <c r="K4">
-        <v>0.5009336149942915</v>
+        <v>0.50093361499429145</v>
       </c>
       <c r="L4">
-        <v>0.4810418733237511</v>
+        <v>0.48104187332375109</v>
       </c>
       <c r="M4">
-        <v>0.4986463538127698</v>
+        <v>0.49864635381276978</v>
       </c>
       <c r="N4">
         <v>0.502717359409661</v>
       </c>
       <c r="O4">
-        <v>0.4951322311712065</v>
+        <v>0.49513223117120653</v>
       </c>
       <c r="P4">
-        <v>0.4982876016280021</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.49828760162800212</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>19</v>
       </c>
       <c r="B5">
-        <v>0.5389219029860139</v>
+        <v>0.53892190298601395</v>
       </c>
       <c r="C5">
-        <v>0.541523266835386</v>
+        <v>0.54152326683538599</v>
       </c>
       <c r="D5">
-        <v>0.5437042431343457</v>
+        <v>0.54370424313434573</v>
       </c>
       <c r="E5">
-        <v>0.534319104006018</v>
+        <v>0.53431910400601801</v>
       </c>
       <c r="F5">
-        <v>0.5301908083828203</v>
+        <v>0.53019080838282029</v>
       </c>
       <c r="G5">
         <v>0.5337599823395186</v>
       </c>
       <c r="H5">
-        <v>0.5295490222111305</v>
+        <v>0.52954902221113054</v>
       </c>
       <c r="I5">
-        <v>0.5194847311823065</v>
+        <v>0.51948473118230654</v>
       </c>
       <c r="J5">
         <v>0.4973113771447033</v>
       </c>
       <c r="K5">
-        <v>0.4900683157093368</v>
+        <v>0.49006831570933679</v>
       </c>
       <c r="L5">
-        <v>0.481402376114289</v>
+        <v>0.48140237611428899</v>
       </c>
       <c r="M5">
-        <v>0.4687850483305905</v>
+        <v>0.46878504833059048</v>
       </c>
       <c r="N5">
-        <v>0.4661282677211661</v>
+        <v>0.46612826772116611</v>
       </c>
       <c r="O5">
         <v>0.4512282293001838</v>
       </c>
       <c r="P5">
-        <v>0.4641135078667948</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
-        </is>
+        <v>0.46411350786679478</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>20</v>
       </c>
       <c r="B6">
         <v>0.540261238234097</v>
@@ -657,395 +845,381 @@
         <v>0.5464788514943435</v>
       </c>
       <c r="D6">
-        <v>0.5503786292504989</v>
+        <v>0.55037862925049885</v>
       </c>
       <c r="E6">
-        <v>0.5338592114300785</v>
+        <v>0.53385921143007853</v>
       </c>
       <c r="F6">
-        <v>0.5551508513931986</v>
+        <v>0.55515085139319864</v>
       </c>
       <c r="G6">
-        <v>0.5230284422613855</v>
+        <v>0.52302844226138545</v>
       </c>
       <c r="H6">
-        <v>0.5292473662714025</v>
+        <v>0.52924736627140245</v>
       </c>
       <c r="I6">
-        <v>0.5058452333838866</v>
+        <v>0.50584523338388665</v>
       </c>
       <c r="J6">
-        <v>0.5012998346163905</v>
+        <v>0.50129983461639049</v>
       </c>
       <c r="K6">
-        <v>0.4889448390810353</v>
+        <v>0.48894483908103531</v>
       </c>
       <c r="L6">
-        <v>0.45627180651133</v>
+        <v>0.45627180651132998</v>
       </c>
       <c r="M6">
         <v>0.4219744037498977</v>
       </c>
       <c r="N6">
-        <v>0.396340804594438</v>
+        <v>0.39634080459443799</v>
       </c>
       <c r="O6">
-        <v>0.395331215606972</v>
+        <v>0.39533121560697199</v>
       </c>
       <c r="P6">
-        <v>0.4283443822509617</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_</t>
-        </is>
+        <v>0.42834438225096172</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>21</v>
       </c>
       <c r="B7">
-        <v>0.3806537974971714</v>
+        <v>0.38065379749717138</v>
       </c>
       <c r="C7">
-        <v>0.5301825779362587</v>
+        <v>0.53018257793625867</v>
       </c>
       <c r="D7">
-        <v>0.6077879810773252</v>
+        <v>0.60778798107732523</v>
       </c>
       <c r="E7">
         <v>0.6493116816476785</v>
       </c>
       <c r="F7">
-        <v>0.6694407795883752</v>
+        <v>0.66944077958837522</v>
       </c>
       <c r="G7">
-        <v>0.6821379694158413</v>
+        <v>0.68213796941584126</v>
       </c>
       <c r="H7">
-        <v>0.6655855811292304</v>
+        <v>0.66558558112923039</v>
       </c>
       <c r="I7">
-        <v>0.6545242697446313</v>
+        <v>0.65452426974463129</v>
       </c>
       <c r="J7">
-        <v>0.6395330274895683</v>
+        <v>0.63953302748956831</v>
       </c>
       <c r="K7">
-        <v>0.6410496629151763</v>
+        <v>0.64104966291517629</v>
       </c>
       <c r="L7">
-        <v>0.5836191372190078</v>
+        <v>0.58361913721900782</v>
       </c>
       <c r="M7">
-        <v>0.5848690888044972</v>
+        <v>0.58486908880449717</v>
       </c>
       <c r="N7">
-        <v>0.599497024017636</v>
+        <v>0.59949702401763605</v>
       </c>
       <c r="O7">
-        <v>0.5978696605321173</v>
+        <v>0.59786966053211732</v>
       </c>
       <c r="P7">
-        <v>0.59741397258361</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
-        </is>
+        <v>0.59741397258360995</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>22</v>
       </c>
       <c r="B8">
-        <v>0.4401842476817213</v>
+        <v>0.44018424768172132</v>
       </c>
       <c r="C8">
-        <v>0.5106895266558933</v>
+        <v>0.51068952665589329</v>
       </c>
       <c r="D8">
         <v>0.5630750579269731</v>
       </c>
       <c r="E8">
-        <v>0.5839620532976921</v>
+        <v>0.58396205329769213</v>
       </c>
       <c r="F8">
-        <v>0.5874929772862156</v>
+        <v>0.58749297728621563</v>
       </c>
       <c r="G8">
-        <v>0.5825512550133697</v>
+        <v>0.58255125501336968</v>
       </c>
       <c r="H8">
-        <v>0.5955899244774183</v>
+        <v>0.59558992447741832</v>
       </c>
       <c r="I8">
-        <v>0.6032695275673484</v>
+        <v>0.60326952756734842</v>
       </c>
       <c r="J8">
-        <v>0.5444851840854016</v>
+        <v>0.54448518408540159</v>
       </c>
       <c r="K8">
-        <v>0.5088457945992551</v>
+        <v>0.50884579459925505</v>
       </c>
       <c r="L8">
-        <v>0.505094871108335</v>
+        <v>0.50509487110833495</v>
       </c>
       <c r="M8">
-        <v>0.5171551297239577</v>
+        <v>0.51715512972395772</v>
       </c>
       <c r="N8">
-        <v>0.542344519491861</v>
+        <v>0.54234451949186102</v>
       </c>
       <c r="O8">
-        <v>0.5225387952974331</v>
+        <v>0.52253879529743308</v>
       </c>
       <c r="P8">
-        <v>0.526671407710306</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
-        </is>
+        <v>0.52667140771030596</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>23</v>
       </c>
       <c r="B9">
-        <v>0.4419605500809753</v>
+        <v>0.44196055008097529</v>
       </c>
       <c r="C9">
-        <v>0.5120091412728218</v>
+        <v>0.51200914127282182</v>
       </c>
       <c r="D9">
-        <v>0.5588997155910935</v>
+        <v>0.55889971559109353</v>
       </c>
       <c r="E9">
-        <v>0.576551642712759</v>
+        <v>0.57655164271275905</v>
       </c>
       <c r="F9">
-        <v>0.5834913743527498</v>
+        <v>0.58349137435274978</v>
       </c>
       <c r="G9">
-        <v>0.5797993828358745</v>
+        <v>0.57979938283587451</v>
       </c>
       <c r="H9">
         <v>0.5884408771888896</v>
       </c>
       <c r="I9">
-        <v>0.5981523903936484</v>
+        <v>0.59815239039364843</v>
       </c>
       <c r="J9">
-        <v>0.5613982890361099</v>
+        <v>0.56139828903610989</v>
       </c>
       <c r="K9">
-        <v>0.5257544390471132</v>
+        <v>0.52575443904711316</v>
       </c>
       <c r="L9">
-        <v>0.5068484226734509</v>
+        <v>0.50684842267345087</v>
       </c>
       <c r="M9">
-        <v>0.5215293499257525</v>
+        <v>0.52152934992575251</v>
       </c>
       <c r="N9">
-        <v>0.5507361497147111</v>
+        <v>0.55073614971471108</v>
       </c>
       <c r="O9">
-        <v>0.5329743291016908</v>
+        <v>0.53297432910169085</v>
       </c>
       <c r="P9">
-        <v>0.530841853360056</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
-        </is>
+        <v>0.53084185336005596</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>24</v>
       </c>
       <c r="B10">
-        <v>0.4404490939130389</v>
+        <v>0.44044909391303888</v>
       </c>
       <c r="C10">
-        <v>0.5118582249273035</v>
+        <v>0.51185822492730348</v>
       </c>
       <c r="D10">
-        <v>0.5590323171406313</v>
+        <v>0.55903231714063129</v>
       </c>
       <c r="E10">
-        <v>0.578786794963045</v>
+        <v>0.57878679496304497</v>
       </c>
       <c r="F10">
-        <v>0.5800583751333533</v>
+        <v>0.58005837513335334</v>
       </c>
       <c r="G10">
-        <v>0.5787481312532073</v>
+        <v>0.57874813125320734</v>
       </c>
       <c r="H10">
-        <v>0.5870756333883096</v>
+        <v>0.58707563338830959</v>
       </c>
       <c r="I10">
-        <v>0.5985313930260059</v>
+        <v>0.59853139302600589</v>
       </c>
       <c r="J10">
-        <v>0.5607381666627412</v>
+        <v>0.56073816666274123</v>
       </c>
       <c r="K10">
-        <v>0.5321472103936903</v>
+        <v>0.53214721039369028</v>
       </c>
       <c r="L10">
-        <v>0.511667308750234</v>
+        <v>0.51166730875023403</v>
       </c>
       <c r="M10">
-        <v>0.5259194774790921</v>
+        <v>0.52591947747909207</v>
       </c>
       <c r="N10">
-        <v>0.5561457459308634</v>
+        <v>0.55614574593086341</v>
       </c>
       <c r="O10">
-        <v>0.5502095419990705</v>
+        <v>0.55020954199907046</v>
       </c>
       <c r="P10">
-        <v>0.5440670325948485</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-        </is>
+        <v>0.54406703259484845</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>25</v>
       </c>
       <c r="B11">
-        <v>0.4412516173696371</v>
+        <v>0.44125161736963708</v>
       </c>
       <c r="C11">
-        <v>0.5107643333076425</v>
+        <v>0.51076433330764248</v>
       </c>
       <c r="D11">
-        <v>0.5605424472175966</v>
+        <v>0.56054244721759661</v>
       </c>
       <c r="E11">
-        <v>0.578369115034134</v>
+        <v>0.57836911503413402</v>
       </c>
       <c r="F11">
-        <v>0.5833786295907348</v>
+        <v>0.58337862959073483</v>
       </c>
       <c r="G11">
-        <v>0.5759383148595066</v>
+        <v>0.57593831485950664</v>
       </c>
       <c r="H11">
-        <v>0.5866244961516219</v>
+        <v>0.58662449615162193</v>
       </c>
       <c r="I11">
-        <v>0.5998655389785345</v>
+        <v>0.59986553897853445</v>
       </c>
       <c r="J11">
-        <v>0.5627624294705943</v>
+        <v>0.56276242947059429</v>
       </c>
       <c r="K11">
-        <v>0.5328617817895163</v>
+        <v>0.53286178178951626</v>
       </c>
       <c r="L11">
-        <v>0.5172063126640827</v>
+        <v>0.51720631266408268</v>
       </c>
       <c r="M11">
-        <v>0.5313431276902648</v>
+        <v>0.53134312769026482</v>
       </c>
       <c r="N11">
-        <v>0.5517092771722092</v>
+        <v>0.55170927717220919</v>
       </c>
       <c r="O11">
-        <v>0.5356633014622554</v>
+        <v>0.53566330146225538</v>
       </c>
       <c r="P11">
-        <v>0.5489341593633549</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.54893415936335488</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>26</v>
       </c>
       <c r="B12">
-        <v>0.5513271741291003</v>
+        <v>0.55132717412910026</v>
       </c>
       <c r="C12">
-        <v>0.5594085247646208</v>
+        <v>0.55940852476462077</v>
       </c>
       <c r="D12">
-        <v>0.5644352342445524</v>
+        <v>0.56443523424455244</v>
       </c>
       <c r="E12">
-        <v>0.5678321195523217</v>
+        <v>0.56783211955232171</v>
       </c>
       <c r="F12">
-        <v>0.5775378701619014</v>
+        <v>0.57753787016190139</v>
       </c>
       <c r="G12">
-        <v>0.5815579456056532</v>
+        <v>0.58155794560565321</v>
       </c>
       <c r="H12">
-        <v>0.5805244136160326</v>
+        <v>0.58052441361603258</v>
       </c>
       <c r="I12">
-        <v>0.5695313262496561</v>
+        <v>0.56953132624965608</v>
       </c>
       <c r="J12">
-        <v>0.5561298435636408</v>
+        <v>0.55612984356364081</v>
       </c>
       <c r="K12">
-        <v>0.5363649380976721</v>
+        <v>0.53636493809767205</v>
       </c>
       <c r="L12">
-        <v>0.5072767301087306</v>
+        <v>0.50727673010873064</v>
       </c>
       <c r="M12">
-        <v>0.480353221909856</v>
+        <v>0.48035322190985602</v>
       </c>
       <c r="N12">
         <v>0.4695611329375261</v>
       </c>
       <c r="O12">
-        <v>0.4535414482770275</v>
+        <v>0.45354144827702753</v>
       </c>
       <c r="P12">
         <v>0.4427295121923342</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
-        </is>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>27</v>
       </c>
       <c r="B13">
-        <v>0.5486929991860214</v>
+        <v>0.54869299918602144</v>
       </c>
       <c r="C13">
-        <v>0.568923044880122</v>
+        <v>0.56892304488012202</v>
       </c>
       <c r="D13">
-        <v>0.5823993620083299</v>
+        <v>0.58239936200832987</v>
       </c>
       <c r="E13">
-        <v>0.5869321203668049</v>
+        <v>0.58693212036680487</v>
       </c>
       <c r="F13">
-        <v>0.5780127633948215</v>
+        <v>0.57801276339482155</v>
       </c>
       <c r="G13">
-        <v>0.5718971243963841</v>
+        <v>0.57189712439638407</v>
       </c>
       <c r="H13">
-        <v>0.5696614950450636</v>
+        <v>0.56966149504506358</v>
       </c>
       <c r="I13">
-        <v>0.5515970905533386</v>
+        <v>0.55159709055333861</v>
       </c>
       <c r="J13">
-        <v>0.5400150474699308</v>
+        <v>0.54001504746993079</v>
       </c>
       <c r="K13">
         <v>0.5107695444838859</v>
       </c>
       <c r="L13">
-        <v>0.4988693327655511</v>
+        <v>0.49886933276555112</v>
       </c>
       <c r="M13">
         <v>0.4906980696922138</v>
@@ -1054,387 +1228,371 @@
         <v>0.4805763056372066</v>
       </c>
       <c r="O13">
-        <v>0.4642091462235045</v>
+        <v>0.46420914622350451</v>
       </c>
       <c r="P13">
-        <v>0.4337859401506434</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-        </is>
+        <v>0.43378594015064342</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>28</v>
       </c>
       <c r="B14">
-        <v>0.3831549493137815</v>
+        <v>0.38315494931378152</v>
       </c>
       <c r="C14">
-        <v>0.5326715420184764</v>
+        <v>0.53267154201847644</v>
       </c>
       <c r="D14">
         <v>0.6081578359023232</v>
       </c>
       <c r="E14">
-        <v>0.6497349859536724</v>
+        <v>0.64973498595367241</v>
       </c>
       <c r="F14">
-        <v>0.6678626033100127</v>
+        <v>0.66786260331001268</v>
       </c>
       <c r="G14">
         <v>0.6792359727541557</v>
       </c>
       <c r="H14">
-        <v>0.6648083116761072</v>
+        <v>0.66480831167610721</v>
       </c>
       <c r="I14">
         <v>0.6560612022626332</v>
       </c>
       <c r="J14">
-        <v>0.6434952506838564</v>
+        <v>0.64349525068385638</v>
       </c>
       <c r="K14">
-        <v>0.6430802013001296</v>
+        <v>0.64308020130012955</v>
       </c>
       <c r="L14">
         <v>0.5831585284173274</v>
       </c>
       <c r="M14">
-        <v>0.5669236102844672</v>
+        <v>0.56692361028446725</v>
       </c>
       <c r="N14">
-        <v>0.5768250110139259</v>
+        <v>0.57682501101392591</v>
       </c>
       <c r="O14">
-        <v>0.5797816292624398</v>
+        <v>0.57978162926243981</v>
       </c>
       <c r="P14">
-        <v>0.5972838333936233</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-        </is>
+        <v>0.59728383339362334</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>29</v>
       </c>
       <c r="B15">
-        <v>0.3814368270436743</v>
+        <v>0.38143682704367432</v>
       </c>
       <c r="C15">
-        <v>0.5304256336352624</v>
+        <v>0.53042563363526241</v>
       </c>
       <c r="D15">
-        <v>0.6079318565118894</v>
+        <v>0.60793185651188941</v>
       </c>
       <c r="E15">
-        <v>0.6509135502238955</v>
+        <v>0.65091355022389552</v>
       </c>
       <c r="F15">
-        <v>0.6684285636624275</v>
+        <v>0.66842856366242753</v>
       </c>
       <c r="G15">
-        <v>0.6791838973812823</v>
+        <v>0.67918389738128226</v>
       </c>
       <c r="H15">
-        <v>0.6653501009303751</v>
+        <v>0.66535010093037505</v>
       </c>
       <c r="I15">
-        <v>0.6557360446970216</v>
+        <v>0.65573604469702163</v>
       </c>
       <c r="J15">
-        <v>0.6434554829162148</v>
+        <v>0.64345548291621479</v>
       </c>
       <c r="K15">
-        <v>0.6426878860504561</v>
+        <v>0.64268788605045613</v>
       </c>
       <c r="L15">
-        <v>0.5858919569028972</v>
+        <v>0.58589195690289719</v>
       </c>
       <c r="M15">
-        <v>0.5678332221218503</v>
+        <v>0.56783322212185028</v>
       </c>
       <c r="N15">
-        <v>0.5723686502684864</v>
+        <v>0.57236865026848638</v>
       </c>
       <c r="O15">
-        <v>0.573781971889707</v>
+        <v>0.57378197188970703</v>
       </c>
       <c r="P15">
-        <v>0.5918703559213001</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
-        </is>
+        <v>0.59187035592130011</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>30</v>
       </c>
       <c r="B16">
-        <v>0.3835497828782048</v>
+        <v>0.38354978287820479</v>
       </c>
       <c r="C16">
-        <v>0.5341487552931831</v>
+        <v>0.53414875529318306</v>
       </c>
       <c r="D16">
-        <v>0.6141192927800846</v>
+        <v>0.61411929278008459</v>
       </c>
       <c r="E16">
-        <v>0.6522663181593077</v>
+        <v>0.65226631815930769</v>
       </c>
       <c r="F16">
-        <v>0.6709756761931375</v>
+        <v>0.67097567619313747</v>
       </c>
       <c r="G16">
         <v>0.6808441646382879</v>
       </c>
       <c r="H16">
-        <v>0.6671118641920505</v>
+        <v>0.66711186419205049</v>
       </c>
       <c r="I16">
-        <v>0.6581370805928646</v>
+        <v>0.65813708059286458</v>
       </c>
       <c r="J16">
-        <v>0.6456440232319102</v>
+        <v>0.64564402323191017</v>
       </c>
       <c r="K16">
-        <v>0.6439847461910861</v>
+        <v>0.64398474619108614</v>
       </c>
       <c r="L16">
-        <v>0.5886526497493335</v>
+        <v>0.58865264974933351</v>
       </c>
       <c r="M16">
-        <v>0.5734226749831621</v>
+        <v>0.57342267498316213</v>
       </c>
       <c r="N16">
-        <v>0.5765230245727326</v>
+        <v>0.57652302457273263</v>
       </c>
       <c r="O16">
-        <v>0.5760379110620623</v>
+        <v>0.57603791106206226</v>
       </c>
       <c r="P16">
-        <v>0.5897782135313985</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-        </is>
+        <v>0.58977821353139848</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>31</v>
       </c>
       <c r="B17">
-        <v>0.3847815067943198</v>
+        <v>0.38478150679431983</v>
       </c>
       <c r="C17">
-        <v>0.533823313470938</v>
+        <v>0.53382331347093803</v>
       </c>
       <c r="D17">
-        <v>0.6102005480247564</v>
+        <v>0.61020054802475643</v>
       </c>
       <c r="E17">
-        <v>0.6494109704472127</v>
+        <v>0.64941097044721274</v>
       </c>
       <c r="F17">
-        <v>0.6665079913661093</v>
+        <v>0.66650799136610928</v>
       </c>
       <c r="G17">
-        <v>0.679379193452786</v>
+        <v>0.67937919345278597</v>
       </c>
       <c r="H17">
-        <v>0.6648389360846445</v>
+        <v>0.66483893608464451</v>
       </c>
       <c r="I17">
-        <v>0.6571043450109091</v>
+        <v>0.65710434501090909</v>
       </c>
       <c r="J17">
-        <v>0.6431808751241975</v>
+        <v>0.64318087512419753</v>
       </c>
       <c r="K17">
-        <v>0.6427923126248353</v>
+        <v>0.64279231262483527</v>
       </c>
       <c r="L17">
-        <v>0.5863961454212434</v>
+        <v>0.58639614542124341</v>
       </c>
       <c r="M17">
-        <v>0.5698660038929247</v>
+        <v>0.56986600389292474</v>
       </c>
       <c r="N17">
-        <v>0.5779349858007052</v>
+        <v>0.57793498580070524</v>
       </c>
       <c r="O17">
-        <v>0.5827940421740683</v>
+        <v>0.58279404217406827</v>
       </c>
       <c r="P17">
         <v>0.5981478747412341</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>32</v>
       </c>
       <c r="B18">
         <v>0.5527824665139438</v>
       </c>
       <c r="C18">
-        <v>0.559417771529966</v>
+        <v>0.55941777152996597</v>
       </c>
       <c r="D18">
-        <v>0.564400305596219</v>
+        <v>0.56440030559621901</v>
       </c>
       <c r="E18">
         <v>0.5673516945961472</v>
       </c>
       <c r="F18">
-        <v>0.589589756993725</v>
+        <v>0.58958975699372496</v>
       </c>
       <c r="G18">
-        <v>0.5814416562294231</v>
+        <v>0.58144165622942312</v>
       </c>
       <c r="H18">
-        <v>0.5906425413393139</v>
+        <v>0.59064254133931393</v>
       </c>
       <c r="I18">
-        <v>0.5812625873813319</v>
+        <v>0.58126258738133185</v>
       </c>
       <c r="J18">
-        <v>0.58470657444823</v>
+        <v>0.58470657444823004</v>
       </c>
       <c r="K18">
-        <v>0.5814344542972982</v>
+        <v>0.58143445429729823</v>
       </c>
       <c r="L18">
-        <v>0.5790257629812999</v>
+        <v>0.57902576298129993</v>
       </c>
       <c r="M18">
-        <v>0.5689255802265579</v>
+        <v>0.56892558022655793</v>
       </c>
       <c r="N18">
-        <v>0.5672711296353491</v>
+        <v>0.56727112963534909</v>
       </c>
       <c r="O18">
-        <v>0.5481581267978141</v>
+        <v>0.54815812679781406</v>
       </c>
       <c r="P18">
-        <v>0.5493181893236398</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
-        </is>
+        <v>0.54931818932363985</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>33</v>
       </c>
       <c r="B19">
-        <v>0.5537170677043536</v>
+        <v>0.55371706770435358</v>
       </c>
       <c r="C19">
         <v>0.5642447750806886</v>
       </c>
       <c r="D19">
-        <v>0.5706933379966727</v>
+        <v>0.57069333799667266</v>
       </c>
       <c r="E19">
-        <v>0.5620224860294386</v>
+        <v>0.56202248602943861</v>
       </c>
       <c r="F19">
-        <v>0.588846584570398</v>
+        <v>0.58884658457039796</v>
       </c>
       <c r="G19">
-        <v>0.5777153939292385</v>
+        <v>0.57771539392923854</v>
       </c>
       <c r="H19">
         <v>0.5873148705445006</v>
       </c>
       <c r="I19">
-        <v>0.5883357777872747</v>
+        <v>0.58833577778727475</v>
       </c>
       <c r="J19">
-        <v>0.5837689223942321</v>
+        <v>0.58376892239423206</v>
       </c>
       <c r="K19">
-        <v>0.5963981775040667</v>
+        <v>0.59639817750406665</v>
       </c>
       <c r="L19">
-        <v>0.5707187123379158</v>
+        <v>0.57071871233791582</v>
       </c>
       <c r="M19">
-        <v>0.5578508955656699</v>
+        <v>0.55785089556566991</v>
       </c>
       <c r="N19">
         <v>0.5491591721006811</v>
       </c>
       <c r="O19">
-        <v>0.5458964632060642</v>
+        <v>0.54589646320606422</v>
       </c>
       <c r="P19">
-        <v>0.5516912098332492</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-        </is>
+        <v>0.55169120983324915</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>34</v>
       </c>
       <c r="B20">
-        <v>0.5549646016536312</v>
+        <v>0.55496460165363115</v>
       </c>
       <c r="C20">
-        <v>0.5667139510820045</v>
+        <v>0.56671395108200451</v>
       </c>
       <c r="D20">
-        <v>0.5814028113793709</v>
+        <v>0.58140281137937089</v>
       </c>
       <c r="E20">
-        <v>0.5680833155134408</v>
+        <v>0.56808331551344082</v>
       </c>
       <c r="F20">
-        <v>0.5779559249858434</v>
+        <v>0.57795592498584336</v>
       </c>
       <c r="G20">
-        <v>0.5960780142132284</v>
+        <v>0.59607801421322837</v>
       </c>
       <c r="H20">
         <v>0.6009754247549246</v>
       </c>
       <c r="I20">
-        <v>0.5997527811770088</v>
+        <v>0.59975278117700881</v>
       </c>
       <c r="J20">
-        <v>0.5978286293759277</v>
+        <v>0.59782862937592773</v>
       </c>
       <c r="K20">
-        <v>0.5958660897615288</v>
+        <v>0.59586608976152877</v>
       </c>
       <c r="L20">
-        <v>0.5801388528488288</v>
+        <v>0.58013885284882882</v>
       </c>
       <c r="M20">
-        <v>0.5570999310984712</v>
+        <v>0.55709993109847122</v>
       </c>
       <c r="N20">
-        <v>0.5474385244952313</v>
+        <v>0.54743852449523134</v>
       </c>
       <c r="O20">
-        <v>0.5695600817718892</v>
+        <v>0.56956008177188922</v>
       </c>
       <c r="P20">
-        <v>0.5701787105636001</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.57017871056360014</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>35</v>
       </c>
       <c r="B21">
-        <v>0.4424305773527772</v>
+        <v>0.44243057735277719</v>
       </c>
       <c r="C21">
-        <v>0.5460433631942804</v>
+        <v>0.54604336319428037</v>
       </c>
       <c r="D21">
         <v>0.5516717297466005</v>
@@ -1443,282 +1601,272 @@
         <v>0.5637977967205231</v>
       </c>
       <c r="F21">
-        <v>0.5604522743106928</v>
+        <v>0.56045227431069278</v>
       </c>
       <c r="G21">
-        <v>0.5467488571075013</v>
+        <v>0.54674885710750132</v>
       </c>
       <c r="H21">
-        <v>0.4837065767419882</v>
+        <v>0.48370657674198819</v>
       </c>
       <c r="I21">
-        <v>0.4647228978956258</v>
+        <v>0.46472289789562582</v>
       </c>
       <c r="J21">
-        <v>0.4650998919713177</v>
+        <v>0.46509989197131768</v>
       </c>
       <c r="K21">
-        <v>0.4415034396828599</v>
+        <v>0.44150343968285988</v>
       </c>
       <c r="L21">
-        <v>0.4150529405450222</v>
+        <v>0.41505294054502218</v>
       </c>
       <c r="M21">
-        <v>0.3792968222481004</v>
+        <v>0.37929682224810041</v>
       </c>
       <c r="N21">
-        <v>0.3390136717253958</v>
+        <v>0.33901367172539582</v>
       </c>
       <c r="O21">
-        <v>0.2881355122727065</v>
+        <v>0.28813551227270651</v>
       </c>
       <c r="P21">
-        <v>0.224714914383698</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.22471491438369801</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>36</v>
       </c>
       <c r="B22">
-        <v>0.4404792582918435</v>
+        <v>0.44047925829184348</v>
       </c>
       <c r="C22">
-        <v>0.5443448896784787</v>
+        <v>0.54434488967847872</v>
       </c>
       <c r="D22">
-        <v>0.5512167777864069</v>
+        <v>0.55121677778640688</v>
       </c>
       <c r="E22">
-        <v>0.5642441602626617</v>
+        <v>0.56424416026266166</v>
       </c>
       <c r="F22">
-        <v>0.5665959140819312</v>
+        <v>0.56659591408193122</v>
       </c>
       <c r="G22">
         <v>0.5692388272138531</v>
       </c>
       <c r="H22">
-        <v>0.5072791051223584</v>
+        <v>0.50727910512235841</v>
       </c>
       <c r="I22">
-        <v>0.4763101251729348</v>
+        <v>0.47631012517293481</v>
       </c>
       <c r="J22">
-        <v>0.4802881722732464</v>
+        <v>0.48028817227324638</v>
       </c>
       <c r="K22">
-        <v>0.4613114154389443</v>
+        <v>0.46131141543894427</v>
       </c>
       <c r="L22">
-        <v>0.4313527455129487</v>
+        <v>0.43135274551294872</v>
       </c>
       <c r="M22">
         <v>0.3942772940030449</v>
       </c>
       <c r="N22">
-        <v>0.3623456465724761</v>
+        <v>0.36234564657247609</v>
       </c>
       <c r="O22">
-        <v>0.3145186649438271</v>
+        <v>0.31451866494382708</v>
       </c>
       <c r="P22">
-        <v>0.2652860907610984</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.26528609076109838</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>37</v>
       </c>
       <c r="B23">
-        <v>0.5495781650981428</v>
+        <v>0.54957816509814283</v>
       </c>
       <c r="C23">
         <v>0.5319445768901544</v>
       </c>
       <c r="D23">
-        <v>0.5475910447337289</v>
+        <v>0.54759104473372888</v>
       </c>
       <c r="E23">
-        <v>0.5614098466303235</v>
+        <v>0.56140984663032345</v>
       </c>
       <c r="F23">
         <v>0.5183878003490684</v>
       </c>
       <c r="G23">
-        <v>0.450050597798058</v>
+        <v>0.45005059779805801</v>
       </c>
       <c r="H23">
-        <v>0.3873946245667121</v>
+        <v>0.38739462456671209</v>
       </c>
       <c r="I23">
-        <v>0.3819148641436186</v>
+        <v>0.38191486414361858</v>
       </c>
       <c r="J23">
-        <v>0.3371252350289478</v>
+        <v>0.33712523502894781</v>
       </c>
       <c r="K23">
-        <v>0.310909861737069</v>
+        <v>0.31090986173706903</v>
       </c>
       <c r="L23">
-        <v>0.2651823977453086</v>
+        <v>0.26518239774530861</v>
       </c>
       <c r="M23">
-        <v>0.2475939109144608</v>
+        <v>0.24759391091446081</v>
       </c>
       <c r="N23">
-        <v>0.1981333007038313</v>
+        <v>0.19813330070383131</v>
       </c>
       <c r="O23">
-        <v>0.1598161239909228</v>
+        <v>0.15981612399092279</v>
       </c>
       <c r="P23">
         <v>0.1058889274038084</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>38</v>
       </c>
       <c r="B24">
-        <v>0.09962268494143753</v>
+        <v>9.9622684941437528E-2</v>
       </c>
       <c r="C24">
-        <v>0.0440513345067477</v>
+        <v>4.4051334506747697E-2</v>
       </c>
       <c r="D24">
-        <v>0.06899141497874064</v>
+        <v>6.8991414978740645E-2</v>
       </c>
       <c r="E24">
-        <v>-0.02243816790475812</v>
+        <v>-2.2438167904758121E-2</v>
       </c>
       <c r="F24">
-        <v>-0.3172516474236515</v>
+        <v>-0.31725164742365147</v>
       </c>
       <c r="G24">
-        <v>-0.2000253706895765</v>
+        <v>-0.20002537068957649</v>
       </c>
       <c r="H24">
-        <v>-0.2592480498317248</v>
+        <v>-0.25924804983172478</v>
       </c>
       <c r="I24">
-        <v>-0.318519343901671</v>
+        <v>-0.31851934390167103</v>
       </c>
       <c r="J24">
-        <v>-0.3949143324479135</v>
+        <v>-0.39491433244791352</v>
       </c>
       <c r="K24">
-        <v>-0.4368302299033583</v>
+        <v>-0.43683022990335829</v>
       </c>
       <c r="L24">
-        <v>-0.4805436869947637</v>
+        <v>-0.48054368699476369</v>
       </c>
       <c r="M24">
-        <v>-0.4684610749511871</v>
+        <v>-0.46846107495118711</v>
       </c>
       <c r="N24">
-        <v>-0.4629456009242219</v>
+        <v>-0.46294560092422188</v>
       </c>
       <c r="O24">
         <v>-0.4852012993549622</v>
       </c>
       <c r="P24">
-        <v>-0.5043637474666717</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>-0.50436374746667167</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>39</v>
       </c>
       <c r="B25">
-        <v>0.07566072400875087</v>
+        <v>7.5660724008750874E-2</v>
       </c>
       <c r="C25">
-        <v>0.03586751955986957</v>
+        <v>3.5867519559869568E-2</v>
       </c>
       <c r="D25">
-        <v>-0.0007719120138557956</v>
+        <v>-7.7191201385579556E-4</v>
       </c>
       <c r="E25">
-        <v>-0.08447490910147587</v>
+        <v>-8.447490910147587E-2</v>
       </c>
       <c r="F25">
         <v>-0.1533089672195472</v>
       </c>
       <c r="G25">
-        <v>-0.2991780555063516</v>
+        <v>-0.29917805550635163</v>
       </c>
       <c r="H25">
         <v>-0.4171656826827827</v>
       </c>
       <c r="I25">
-        <v>-0.5055122254220439</v>
+        <v>-0.50551222542204388</v>
       </c>
       <c r="J25">
-        <v>-0.542987002996988</v>
+        <v>-0.54298700299698799</v>
       </c>
       <c r="K25">
-        <v>-0.5564141226445387</v>
+        <v>-0.55641412264453871</v>
       </c>
       <c r="L25">
-        <v>-0.6354675212628872</v>
+        <v>-0.63546752126288719</v>
       </c>
       <c r="M25">
-        <v>-0.7135770959366955</v>
+        <v>-0.71357709593669549</v>
       </c>
       <c r="N25">
-        <v>-0.7748061840132338</v>
+        <v>-0.77480618401323376</v>
       </c>
       <c r="O25">
         <v>-0.8033320931835588</v>
       </c>
       <c r="P25">
-        <v>-0.8279395489440222</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>-0.82793954894402222</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>40</v>
       </c>
       <c r="B26">
-        <v>0.08245379925242763</v>
+        <v>8.2453799252427629E-2</v>
       </c>
       <c r="C26">
-        <v>0.04967393503878866</v>
+        <v>4.9673935038788662E-2</v>
       </c>
       <c r="D26">
-        <v>0.05390074453108046</v>
+        <v>5.3900744531080458E-2</v>
       </c>
       <c r="E26">
-        <v>-0.01246250494728214</v>
+        <v>-1.2462504947282141E-2</v>
       </c>
       <c r="F26">
         <v>-0.1084617775083942</v>
       </c>
       <c r="G26">
-        <v>-0.1284899745029734</v>
+        <v>-0.12848997450297339</v>
       </c>
       <c r="H26">
         <v>-0.2055737381541094</v>
       </c>
       <c r="I26">
-        <v>-0.1865849155884388</v>
+        <v>-0.18658491558843879</v>
       </c>
       <c r="J26">
-        <v>-0.1271637426029601</v>
+        <v>-0.12716374260296009</v>
       </c>
       <c r="K26">
-        <v>-0.07224224976246023</v>
+        <v>-7.2242249762460228E-2</v>
       </c>
       <c r="L26">
         <v>-0.2301436280648278</v>
@@ -1727,32 +1875,30 @@
         <v>-0.3720972429703267</v>
       </c>
       <c r="N26">
-        <v>-0.3226273117510726</v>
+        <v>-0.32262731175107262</v>
       </c>
       <c r="O26">
         <v>-0.3466396274595987</v>
       </c>
       <c r="P26">
-        <v>-0.356380491667895</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>-0.35638049166789498</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>41</v>
       </c>
       <c r="B27">
-        <v>0.06693538739544472</v>
+        <v>6.6935387395444718E-2</v>
       </c>
       <c r="C27">
-        <v>0.05141585681717636</v>
+        <v>5.1415856817176357E-2</v>
       </c>
       <c r="D27">
-        <v>-0.05271989974848362</v>
+        <v>-5.2719899748483623E-2</v>
       </c>
       <c r="E27">
-        <v>-0.0003519117230431634</v>
+        <v>-3.5191172304316343E-4</v>
       </c>
       <c r="F27">
         <v>-0.1132533091966057</v>
@@ -1761,10 +1907,10 @@
         <v>-0.1065365921175368</v>
       </c>
       <c r="H27">
-        <v>-0.04129337509946363</v>
+        <v>-4.1293375099463632E-2</v>
       </c>
       <c r="I27">
-        <v>-0.03413683208980507</v>
+        <v>-3.4136832089805072E-2</v>
       </c>
       <c r="J27">
         <v>-0.1153147354859461</v>
@@ -1773,1062 +1919,1035 @@
         <v>-0.1989490500709036</v>
       </c>
       <c r="L27">
-        <v>-0.265660495976542</v>
+        <v>-0.26566049597654201</v>
       </c>
       <c r="M27">
-        <v>-0.3453578114132839</v>
+        <v>-0.34535781141328392</v>
       </c>
       <c r="N27">
-        <v>-0.2745780076387571</v>
+        <v>-0.27457800763875712</v>
       </c>
       <c r="O27">
-        <v>-0.3767873185105658</v>
+        <v>-0.37678731851056579</v>
       </c>
       <c r="P27">
-        <v>-0.4220049752747957</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
-        </is>
+        <v>-0.42200497527479569</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>42</v>
       </c>
       <c r="B28">
-        <v>0.5720717409949735</v>
+        <v>0.57207174099497349</v>
       </c>
       <c r="C28">
-        <v>0.6335777756631754</v>
+        <v>0.63357777566317541</v>
       </c>
       <c r="D28">
-        <v>0.6659989936522658</v>
+        <v>0.66599899365226578</v>
       </c>
       <c r="E28">
-        <v>0.6877912300881189</v>
+        <v>0.68779123008811893</v>
       </c>
       <c r="F28">
-        <v>0.6674548507209292</v>
+        <v>0.66745485072092925</v>
       </c>
       <c r="G28">
-        <v>0.6630434480840722</v>
+        <v>0.66304344808407223</v>
       </c>
       <c r="H28">
-        <v>0.661858778274211</v>
+        <v>0.66185877827421102</v>
       </c>
       <c r="I28">
-        <v>0.6441639960009802</v>
+        <v>0.64416399600098018</v>
       </c>
       <c r="J28">
-        <v>0.6651443357914378</v>
+        <v>0.66514433579143784</v>
       </c>
       <c r="K28">
-        <v>0.6741552718179403</v>
+        <v>0.67415527181794033</v>
       </c>
       <c r="L28">
-        <v>0.6604533860261916</v>
+        <v>0.66045338602619164</v>
       </c>
       <c r="M28">
-        <v>0.6330041218195587</v>
+        <v>0.63300412181955867</v>
       </c>
       <c r="N28">
-        <v>0.6043304203154972</v>
+        <v>0.60433042031549722</v>
       </c>
       <c r="O28">
-        <v>0.584551329494999</v>
+        <v>0.58455132949499899</v>
       </c>
       <c r="P28">
         <v>0.54845491333551</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
-        </is>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>43</v>
       </c>
       <c r="B29">
-        <v>0.5727629406097925</v>
+        <v>0.57276294060979249</v>
       </c>
       <c r="C29">
-        <v>0.6378005414177805</v>
+        <v>0.63780054141778053</v>
       </c>
       <c r="D29">
         <v>0.6799487065455172</v>
       </c>
       <c r="E29">
-        <v>0.7120301642587294</v>
+        <v>0.71203016425872945</v>
       </c>
       <c r="F29">
-        <v>0.7041262355908073</v>
+        <v>0.70412623559080734</v>
       </c>
       <c r="G29">
-        <v>0.7167322376209276</v>
+        <v>0.71673223762092764</v>
       </c>
       <c r="H29">
         <v>0.7114679712218186</v>
       </c>
       <c r="I29">
-        <v>0.6972729395976321</v>
+        <v>0.69727293959763215</v>
       </c>
       <c r="J29">
-        <v>0.7323677258113995</v>
+        <v>0.73236772581139953</v>
       </c>
       <c r="K29">
         <v>0.7359475096495055</v>
       </c>
       <c r="L29">
-        <v>0.7367319168087216</v>
+        <v>0.73673191680872163</v>
       </c>
       <c r="M29">
-        <v>0.7182838811433006</v>
+        <v>0.71828388114330055</v>
       </c>
       <c r="N29">
-        <v>0.7040627933702219</v>
+        <v>0.70406279337022193</v>
       </c>
       <c r="O29">
-        <v>0.6804898168922414</v>
+        <v>0.68048981689224142</v>
       </c>
       <c r="P29">
-        <v>0.6524464144602186</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
-        </is>
+        <v>0.65244641446021856</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>44</v>
       </c>
       <c r="B30">
-        <v>0.5875756633608537</v>
+        <v>0.58757566336085365</v>
       </c>
       <c r="C30">
-        <v>0.6196346985724088</v>
+        <v>0.61963469857240883</v>
       </c>
       <c r="D30">
-        <v>0.6542736014329907</v>
+        <v>0.65427360143299074</v>
       </c>
       <c r="E30">
-        <v>0.6836399899222468</v>
+        <v>0.68363998992224684</v>
       </c>
       <c r="F30">
-        <v>0.6658282257554946</v>
+        <v>0.66582822575549461</v>
       </c>
       <c r="G30">
-        <v>0.682267469908662</v>
+        <v>0.68226746990866205</v>
       </c>
       <c r="H30">
-        <v>0.6787213969026543</v>
+        <v>0.67872139690265432</v>
       </c>
       <c r="I30">
-        <v>0.6780328443944316</v>
+        <v>0.67803284439443157</v>
       </c>
       <c r="J30">
-        <v>0.6763444244647536</v>
+        <v>0.67634442446475362</v>
       </c>
       <c r="K30">
-        <v>0.6887487538417819</v>
+        <v>0.68874875384178191</v>
       </c>
       <c r="L30">
-        <v>0.6825393181528668</v>
+        <v>0.68253931815286684</v>
       </c>
       <c r="M30">
         <v>0.6760503328270755</v>
       </c>
       <c r="N30">
-        <v>0.6540336162289199</v>
+        <v>0.65403361622891987</v>
       </c>
       <c r="O30">
-        <v>0.6274794236362566</v>
+        <v>0.62747942363625664</v>
       </c>
       <c r="P30">
-        <v>0.5967940457251966</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-        </is>
+        <v>0.59679404572519656</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>45</v>
       </c>
       <c r="B31">
-        <v>0.5904019416394274</v>
+        <v>0.59040194163942739</v>
       </c>
       <c r="C31">
-        <v>0.6222149305012368</v>
+        <v>0.62221493050123677</v>
       </c>
       <c r="D31">
-        <v>0.6572100290640078</v>
+        <v>0.65721002906400783</v>
       </c>
       <c r="E31">
-        <v>0.6858373006679477</v>
+        <v>0.68583730066794768</v>
       </c>
       <c r="F31">
-        <v>0.668799414844148</v>
+        <v>0.66879941484414795</v>
       </c>
       <c r="G31">
-        <v>0.6836168374903371</v>
+        <v>0.68361683749033708</v>
       </c>
       <c r="H31">
-        <v>0.6800640478423767</v>
+        <v>0.68006404784237673</v>
       </c>
       <c r="I31">
-        <v>0.6751681335365687</v>
+        <v>0.67516813353656868</v>
       </c>
       <c r="J31">
-        <v>0.6665760391789909</v>
+        <v>0.66657603917899089</v>
       </c>
       <c r="K31">
-        <v>0.6712721444433293</v>
+        <v>0.67127214444332928</v>
       </c>
       <c r="L31">
-        <v>0.6685943406663005</v>
+        <v>0.66859434066630052</v>
       </c>
       <c r="M31">
         <v>0.6661836604013287</v>
       </c>
       <c r="N31">
-        <v>0.6479164520376099</v>
+        <v>0.64791645203760995</v>
       </c>
       <c r="O31">
-        <v>0.6289086665877155</v>
+        <v>0.62890866658771549</v>
       </c>
       <c r="P31">
-        <v>0.6363546834980142</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
-        </is>
+        <v>0.63635468349801416</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>46</v>
       </c>
       <c r="B32">
-        <v>0.571721185000255</v>
+        <v>0.57172118500025504</v>
       </c>
       <c r="C32">
-        <v>0.6370572322441513</v>
+        <v>0.63705723224415134</v>
       </c>
       <c r="D32">
-        <v>0.6780731632091722</v>
+        <v>0.67807316320917221</v>
       </c>
       <c r="E32">
-        <v>0.7091088450668094</v>
+        <v>0.70910884506680938</v>
       </c>
       <c r="F32">
-        <v>0.7022276687325343</v>
+        <v>0.70222766873253428</v>
       </c>
       <c r="G32">
-        <v>0.7110656560346139</v>
+        <v>0.71106565603461391</v>
       </c>
       <c r="H32">
         <v>0.7085478818112646</v>
       </c>
       <c r="I32">
-        <v>0.6854222606823488</v>
+        <v>0.68542226068234879</v>
       </c>
       <c r="J32">
-        <v>0.712468165493116</v>
+        <v>0.71246816549311598</v>
       </c>
       <c r="K32">
-        <v>0.7238334116286358</v>
+        <v>0.72383341162863579</v>
       </c>
       <c r="L32">
-        <v>0.7332630772240579</v>
+        <v>0.73326307722405792</v>
       </c>
       <c r="M32">
-        <v>0.7226236025694315</v>
+        <v>0.72262360256943148</v>
       </c>
       <c r="N32">
-        <v>0.7134428321085455</v>
+        <v>0.71344283210854553</v>
       </c>
       <c r="O32">
-        <v>0.7009670133936355</v>
+        <v>0.70096701339363554</v>
       </c>
       <c r="P32">
-        <v>0.6637395428138022</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
-        </is>
+        <v>0.66373954281380221</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>47</v>
       </c>
       <c r="B33">
-        <v>0.569446849498805</v>
+        <v>0.56944684949880497</v>
       </c>
       <c r="C33">
-        <v>0.6341833172876108</v>
+        <v>0.63418331728761079</v>
       </c>
       <c r="D33">
-        <v>0.677609196603815</v>
+        <v>0.67760919660381502</v>
       </c>
       <c r="E33">
-        <v>0.7088241335717431</v>
+        <v>0.70882413357174312</v>
       </c>
       <c r="F33">
-        <v>0.7043914459498813</v>
+        <v>0.70439144594988135</v>
       </c>
       <c r="G33">
-        <v>0.7132607029956968</v>
+        <v>0.71326070299569677</v>
       </c>
       <c r="H33">
-        <v>0.7106607065175539</v>
+        <v>0.71066070651755386</v>
       </c>
       <c r="I33">
-        <v>0.6878006996617853</v>
+        <v>0.68780069966178525</v>
       </c>
       <c r="J33">
-        <v>0.7158528136694752</v>
+        <v>0.71585281366947517</v>
       </c>
       <c r="K33">
-        <v>0.7256153428057721</v>
+        <v>0.72561534280577211</v>
       </c>
       <c r="L33">
-        <v>0.7322659683620565</v>
+        <v>0.73226596836205649</v>
       </c>
       <c r="M33">
-        <v>0.720356575919456</v>
+        <v>0.72035657591945601</v>
       </c>
       <c r="N33">
-        <v>0.7118130790613396</v>
+        <v>0.71181307906133962</v>
       </c>
       <c r="O33">
-        <v>0.6942798216651542</v>
+        <v>0.69427982166515423</v>
       </c>
       <c r="P33">
-        <v>0.6509885602875805</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
-        </is>
+        <v>0.65098856028758045</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>48</v>
       </c>
       <c r="B34">
-        <v>0.5711922665450005</v>
+        <v>0.57119226654500055</v>
       </c>
       <c r="C34">
-        <v>0.6363157043767818</v>
+        <v>0.63631570437678175</v>
       </c>
       <c r="D34">
-        <v>0.6784894045950784</v>
+        <v>0.67848940459507845</v>
       </c>
       <c r="E34">
-        <v>0.7100345566088797</v>
+        <v>0.71003455660887971</v>
       </c>
       <c r="F34">
-        <v>0.7032372447403746</v>
+        <v>0.70323724474037463</v>
       </c>
       <c r="G34">
-        <v>0.7116710708907485</v>
+        <v>0.71167107089074855</v>
       </c>
       <c r="H34">
-        <v>0.7091400894407388</v>
+        <v>0.70914008944073881</v>
       </c>
       <c r="I34">
-        <v>0.6804719959925051</v>
+        <v>0.68047199599250507</v>
       </c>
       <c r="J34">
-        <v>0.7116972744430736</v>
+        <v>0.71169727444307362</v>
       </c>
       <c r="K34">
-        <v>0.7222667818723272</v>
+        <v>0.72226678187232718</v>
       </c>
       <c r="L34">
-        <v>0.7324494421731985</v>
+        <v>0.73244944217319852</v>
       </c>
       <c r="M34">
-        <v>0.7202162130292797</v>
+        <v>0.72021621302927974</v>
       </c>
       <c r="N34">
-        <v>0.7117620618446441</v>
+        <v>0.71176206184464408</v>
       </c>
       <c r="O34">
-        <v>0.6993109626949953</v>
+        <v>0.69931096269499526</v>
       </c>
       <c r="P34">
-        <v>0.6591773541246903</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
-        </is>
+        <v>0.65917735412469025</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>49</v>
       </c>
       <c r="B35">
-        <v>0.5694903926518027</v>
+        <v>0.56949039265180268</v>
       </c>
       <c r="C35">
         <v>0.634932074197879</v>
       </c>
       <c r="D35">
-        <v>0.6772839555934856</v>
+        <v>0.67728395559348564</v>
       </c>
       <c r="E35">
-        <v>0.710203727199622</v>
+        <v>0.71020372719962199</v>
       </c>
       <c r="F35">
-        <v>0.7047257973896459</v>
+        <v>0.70472579738964591</v>
       </c>
       <c r="G35">
-        <v>0.7124729997538473</v>
+        <v>0.71247299975384726</v>
       </c>
       <c r="H35">
-        <v>0.7091179901006494</v>
+        <v>0.70911799010064935</v>
       </c>
       <c r="I35">
-        <v>0.6819954017320728</v>
+        <v>0.68199540173207285</v>
       </c>
       <c r="J35">
-        <v>0.7104291669480021</v>
+        <v>0.71042916694800207</v>
       </c>
       <c r="K35">
-        <v>0.7221389662470333</v>
+        <v>0.72213896624703333</v>
       </c>
       <c r="L35">
-        <v>0.7363393870275592</v>
+        <v>0.73633938702755919</v>
       </c>
       <c r="M35">
-        <v>0.723242464033117</v>
+        <v>0.72324246403311698</v>
       </c>
       <c r="N35">
-        <v>0.7153541875311957</v>
+        <v>0.71535418753119573</v>
       </c>
       <c r="O35">
-        <v>0.7057712399162542</v>
+        <v>0.70577123991625423</v>
       </c>
       <c r="P35">
-        <v>0.6717426541619215</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-        </is>
+        <v>0.67174265416192147</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>50</v>
       </c>
       <c r="B36">
-        <v>0.571268232133147</v>
+        <v>0.57126823213314704</v>
       </c>
       <c r="C36">
-        <v>0.6363891348960782</v>
+        <v>0.63638913489607818</v>
       </c>
       <c r="D36">
-        <v>0.6799520379661437</v>
+        <v>0.67995203796614367</v>
       </c>
       <c r="E36">
-        <v>0.7110012232873646</v>
+        <v>0.71100122328736459</v>
       </c>
       <c r="F36">
-        <v>0.7036207580267959</v>
+        <v>0.70362075802679591</v>
       </c>
       <c r="G36">
-        <v>0.7141817950481383</v>
+        <v>0.71418179504813828</v>
       </c>
       <c r="H36">
-        <v>0.7083059488687553</v>
+        <v>0.70830594886875531</v>
       </c>
       <c r="I36">
-        <v>0.6851497110116611</v>
+        <v>0.68514971101166111</v>
       </c>
       <c r="J36">
-        <v>0.7144916658360854</v>
+        <v>0.71449166583608537</v>
       </c>
       <c r="K36">
-        <v>0.7231179374160679</v>
+        <v>0.72311793741606789</v>
       </c>
       <c r="L36">
-        <v>0.7254647767481888</v>
+        <v>0.72546477674818877</v>
       </c>
       <c r="M36">
-        <v>0.7125036184178992</v>
+        <v>0.71250361841789922</v>
       </c>
       <c r="N36">
-        <v>0.7031033862921147</v>
+        <v>0.70310338629211466</v>
       </c>
       <c r="O36">
-        <v>0.6898047549349487</v>
+        <v>0.68980475493494875</v>
       </c>
       <c r="P36">
-        <v>0.6600618851029408</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
-        </is>
+        <v>0.66006188510294084</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>51</v>
       </c>
       <c r="B37">
-        <v>0.5680803090673567</v>
+        <v>0.56808030906735674</v>
       </c>
       <c r="C37">
-        <v>0.6339222180980434</v>
+        <v>0.63392221809804339</v>
       </c>
       <c r="D37">
-        <v>0.676637025317831</v>
+        <v>0.67663702531783099</v>
       </c>
       <c r="E37">
-        <v>0.7084194939075201</v>
+        <v>0.70841949390752013</v>
       </c>
       <c r="F37">
-        <v>0.7008660401395886</v>
+        <v>0.70086604013958864</v>
       </c>
       <c r="G37">
-        <v>0.7089617019960077</v>
+        <v>0.70896170199600772</v>
       </c>
       <c r="H37">
-        <v>0.704602454192835</v>
+        <v>0.70460245419283496</v>
       </c>
       <c r="I37">
-        <v>0.6847720264219134</v>
+        <v>0.68477202642191337</v>
       </c>
       <c r="J37">
-        <v>0.7130408279063836</v>
+        <v>0.71304082790638357</v>
       </c>
       <c r="K37">
-        <v>0.7174407985413647</v>
+        <v>0.71744079854136467</v>
       </c>
       <c r="L37">
         <v>0.7247470291691579</v>
       </c>
       <c r="M37">
-        <v>0.7129319043357096</v>
+        <v>0.71293190433570963</v>
       </c>
       <c r="N37">
-        <v>0.7049929856212349</v>
+        <v>0.70499298562123491</v>
       </c>
       <c r="O37">
-        <v>0.6926652299946144</v>
+        <v>0.69266522999461444</v>
       </c>
       <c r="P37">
-        <v>0.6590200590257583</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
-        </is>
+        <v>0.65902005902575833</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>52</v>
       </c>
       <c r="B38">
-        <v>0.5710848976024714</v>
+        <v>0.57108489760247139</v>
       </c>
       <c r="C38">
-        <v>0.6360624742099837</v>
+        <v>0.63606247420998374</v>
       </c>
       <c r="D38">
-        <v>0.6790787734068245</v>
+        <v>0.67907877340682454</v>
       </c>
       <c r="E38">
-        <v>0.7107091981835377</v>
+        <v>0.71070919818353773</v>
       </c>
       <c r="F38">
         <v>0.7046399167423022</v>
       </c>
       <c r="G38">
-        <v>0.714875535671299</v>
+        <v>0.71487553567129902</v>
       </c>
       <c r="H38">
         <v>0.7083173703709601</v>
       </c>
       <c r="I38">
-        <v>0.6900797984239339</v>
+        <v>0.69007979842393385</v>
       </c>
       <c r="J38">
-        <v>0.7164700820368465</v>
+        <v>0.71647008203684648</v>
       </c>
       <c r="K38">
-        <v>0.7241155578785063</v>
+        <v>0.72411555787850634</v>
       </c>
       <c r="L38">
-        <v>0.7298456264436706</v>
+        <v>0.72984562644367057</v>
       </c>
       <c r="M38">
         <v>0.7204918999365878</v>
       </c>
       <c r="N38">
-        <v>0.7105392513010869</v>
+        <v>0.71053925130108686</v>
       </c>
       <c r="O38">
-        <v>0.6973691554906161</v>
+        <v>0.69736915549061607</v>
       </c>
       <c r="P38">
-        <v>0.6619549204807229</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-        </is>
+        <v>0.66195492048072291</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>53</v>
       </c>
       <c r="B39">
-        <v>0.5698046820846385</v>
+        <v>0.56980468208463853</v>
       </c>
       <c r="C39">
-        <v>0.6344012924406813</v>
+        <v>0.63440129244068133</v>
       </c>
       <c r="D39">
-        <v>0.6761180736417475</v>
+        <v>0.67611807364174747</v>
       </c>
       <c r="E39">
-        <v>0.7091756331459461</v>
+        <v>0.70917563314594612</v>
       </c>
       <c r="F39">
-        <v>0.7019723887920631</v>
+        <v>0.70197238879206314</v>
       </c>
       <c r="G39">
-        <v>0.710021988473396</v>
+        <v>0.71002198847339604</v>
       </c>
       <c r="H39">
-        <v>0.7070030800213541</v>
+        <v>0.70700308002135415</v>
       </c>
       <c r="I39">
-        <v>0.6833511843376427</v>
+        <v>0.68335118433764275</v>
       </c>
       <c r="J39">
-        <v>0.7118153002270829</v>
+        <v>0.71181530022708295</v>
       </c>
       <c r="K39">
-        <v>0.7210441816882228</v>
+        <v>0.72104418168822282</v>
       </c>
       <c r="L39">
-        <v>0.7278908441611927</v>
+        <v>0.72789084416119265</v>
       </c>
       <c r="M39">
-        <v>0.7167685373570958</v>
+        <v>0.71676853735709578</v>
       </c>
       <c r="N39">
-        <v>0.7083155300489243</v>
+        <v>0.70831553004892434</v>
       </c>
       <c r="O39">
-        <v>0.6995558082844011</v>
+        <v>0.69955580828440111</v>
       </c>
       <c r="P39">
-        <v>0.6650419057883826</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-        </is>
+        <v>0.66504190578838263</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>54</v>
       </c>
       <c r="B40">
-        <v>0.569744855644274</v>
+        <v>0.56974485564427402</v>
       </c>
       <c r="C40">
-        <v>0.6361217598285194</v>
+        <v>0.63612175982851937</v>
       </c>
       <c r="D40">
-        <v>0.6796932783047258</v>
+        <v>0.67969327830472581</v>
       </c>
       <c r="E40">
-        <v>0.7112445080347117</v>
+        <v>0.71124450803471173</v>
       </c>
       <c r="F40">
-        <v>0.7064235053993987</v>
+        <v>0.70642350539939869</v>
       </c>
       <c r="G40">
-        <v>0.7142560296484601</v>
+        <v>0.71425602964846013</v>
       </c>
       <c r="H40">
         <v>0.7096919180056086</v>
       </c>
       <c r="I40">
-        <v>0.6846343410554019</v>
+        <v>0.68463434105540188</v>
       </c>
       <c r="J40">
         <v>0.7141645397607751</v>
       </c>
       <c r="K40">
-        <v>0.7226419103803411</v>
+        <v>0.72264191038034109</v>
       </c>
       <c r="L40">
-        <v>0.735543509783713</v>
+        <v>0.73554350978371297</v>
       </c>
       <c r="M40">
-        <v>0.7226401857211646</v>
+        <v>0.72264018572116462</v>
       </c>
       <c r="N40">
-        <v>0.7136858127625393</v>
+        <v>0.71368581276253928</v>
       </c>
       <c r="O40">
-        <v>0.7026332986069664</v>
+        <v>0.70263329860696644</v>
       </c>
       <c r="P40">
-        <v>0.6587498018656204</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.65874980186562038</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>55</v>
       </c>
       <c r="B41">
-        <v>0.5912959415536931</v>
+        <v>0.59129594155369314</v>
       </c>
       <c r="C41">
-        <v>0.6489321303171531</v>
+        <v>0.64893213031715313</v>
       </c>
       <c r="D41">
-        <v>0.6973323392345365</v>
+        <v>0.69733233923453652</v>
       </c>
       <c r="E41">
-        <v>0.69254362208177</v>
+        <v>0.69254362208177001</v>
       </c>
       <c r="F41">
-        <v>0.6581280236451588</v>
+        <v>0.65812802364515877</v>
       </c>
       <c r="G41">
-        <v>0.6034331883180802</v>
+        <v>0.60343318831808024</v>
       </c>
       <c r="H41">
-        <v>0.6116797490230101</v>
+        <v>0.61167974902301014</v>
       </c>
       <c r="I41">
         <v>0.5993492403434717</v>
       </c>
       <c r="J41">
-        <v>0.5820461575138389</v>
+        <v>0.58204615751383892</v>
       </c>
       <c r="K41">
-        <v>0.5795001797824337</v>
+        <v>0.57950017978243373</v>
       </c>
       <c r="L41">
-        <v>0.5597117745658624</v>
+        <v>0.55971177456586241</v>
       </c>
       <c r="M41">
-        <v>0.5612638093882382</v>
+        <v>0.56126380938823817</v>
       </c>
       <c r="N41">
-        <v>0.5458448351766744</v>
+        <v>0.54584483517667437</v>
       </c>
       <c r="O41">
-        <v>0.5278052596319177</v>
+        <v>0.52780525963191771</v>
       </c>
       <c r="P41">
-        <v>0.5173087835161015</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
-        </is>
+        <v>0.51730878351610154</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>56</v>
       </c>
       <c r="B42">
-        <v>0.5925234334289063</v>
+        <v>0.59252343342890634</v>
       </c>
       <c r="C42">
-        <v>0.6607995054515191</v>
+        <v>0.66079950545151911</v>
       </c>
       <c r="D42">
         <v>0.707637900473716</v>
       </c>
       <c r="E42">
-        <v>0.7044187806685958</v>
+        <v>0.70441878066859576</v>
       </c>
       <c r="F42">
-        <v>0.6679297516798774</v>
+        <v>0.66792975167987745</v>
       </c>
       <c r="G42">
-        <v>0.6257257520003281</v>
+        <v>0.62572575200032809</v>
       </c>
       <c r="H42">
-        <v>0.650615578555671</v>
+        <v>0.65061557855567098</v>
       </c>
       <c r="I42">
-        <v>0.645692811487764</v>
+        <v>0.64569281148776403</v>
       </c>
       <c r="J42">
-        <v>0.6477305593477838</v>
+        <v>0.64773055934778379</v>
       </c>
       <c r="K42">
-        <v>0.6684874849178665</v>
+        <v>0.66848748491786647</v>
       </c>
       <c r="L42">
-        <v>0.6675667647996001</v>
+        <v>0.66756676479960009</v>
       </c>
       <c r="M42">
-        <v>0.6593659887492396</v>
+        <v>0.65936598874923957</v>
       </c>
       <c r="N42">
         <v>0.6558427640331782</v>
       </c>
       <c r="O42">
-        <v>0.6383585937132464</v>
+        <v>0.63835859371324644</v>
       </c>
       <c r="P42">
-        <v>0.6053424185751629</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-        </is>
+        <v>0.60534241857516291</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>57</v>
       </c>
       <c r="B43">
-        <v>0.5945412748035567</v>
+        <v>0.59454127480355667</v>
       </c>
       <c r="C43">
-        <v>0.6584255221453106</v>
+        <v>0.65842552214531058</v>
       </c>
       <c r="D43">
-        <v>0.7070591245690631</v>
+        <v>0.70705912456906306</v>
       </c>
       <c r="E43">
-        <v>0.7021178135730096</v>
+        <v>0.70211781357300962</v>
       </c>
       <c r="F43">
-        <v>0.6701248771142225</v>
+        <v>0.67012487711422253</v>
       </c>
       <c r="G43">
-        <v>0.628162714025192</v>
+        <v>0.62816271402519197</v>
       </c>
       <c r="H43">
-        <v>0.6587863423493472</v>
+        <v>0.65878634234934719</v>
       </c>
       <c r="I43">
-        <v>0.654989101005622</v>
+        <v>0.65498910100562202</v>
       </c>
       <c r="J43">
-        <v>0.6503579661347668</v>
+        <v>0.65035796613476682</v>
       </c>
       <c r="K43">
-        <v>0.65784930434429</v>
+        <v>0.65784930434429001</v>
       </c>
       <c r="L43">
-        <v>0.6591695900329393</v>
+        <v>0.65916959003293929</v>
       </c>
       <c r="M43">
-        <v>0.65398580721724</v>
+        <v>0.65398580721723998</v>
       </c>
       <c r="N43">
-        <v>0.6559120028736932</v>
+        <v>0.65591200287369322</v>
       </c>
       <c r="O43">
-        <v>0.6494741284329494</v>
+        <v>0.64947412843294938</v>
       </c>
       <c r="P43">
-        <v>0.626086414519834</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-        </is>
+        <v>0.62608641451983404</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>58</v>
       </c>
       <c r="B44">
-        <v>0.551671683485314</v>
+        <v>0.55167168348531403</v>
       </c>
       <c r="C44">
-        <v>0.5464456552148095</v>
+        <v>0.54644565521480948</v>
       </c>
       <c r="D44">
-        <v>0.5841049372727039</v>
+        <v>0.58410493727270385</v>
       </c>
       <c r="E44">
-        <v>0.6425907595586609</v>
+        <v>0.64259075955866085</v>
       </c>
       <c r="F44">
-        <v>0.6433276677851117</v>
+        <v>0.64332766778511175</v>
       </c>
       <c r="G44">
-        <v>0.6443799374409058</v>
+        <v>0.64437993744090583</v>
       </c>
       <c r="H44">
-        <v>0.6207893468316202</v>
+        <v>0.62078934683162024</v>
       </c>
       <c r="I44">
-        <v>0.6164797612359625</v>
+        <v>0.61647976123596249</v>
       </c>
       <c r="J44">
-        <v>0.6059871891823301</v>
+        <v>0.60598718918233008</v>
       </c>
       <c r="K44">
-        <v>0.5763995150693959</v>
+        <v>0.57639951506939591</v>
       </c>
       <c r="L44">
-        <v>0.5355067344132265</v>
+        <v>0.53550673441322649</v>
       </c>
       <c r="M44">
         <v>0.498059574129741</v>
       </c>
       <c r="N44">
-        <v>0.4651111175393141</v>
+        <v>0.46511111753931411</v>
       </c>
       <c r="O44">
         <v>0.4310097701313374</v>
       </c>
       <c r="P44">
-        <v>0.3842183005825064</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(1,3,5)_</t>
-        </is>
+        <v>0.38421830058250639</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>59</v>
       </c>
       <c r="B45">
         <v>0.5386367630112614</v>
       </c>
       <c r="C45">
-        <v>0.579179263272051</v>
+        <v>0.57917926327205105</v>
       </c>
       <c r="D45">
-        <v>0.5600157454845799</v>
+        <v>0.56001574548457989</v>
       </c>
       <c r="E45">
-        <v>0.5291910363280133</v>
+        <v>0.52919103632801334</v>
       </c>
       <c r="F45">
-        <v>0.4803023232812113</v>
+        <v>0.48030232328121131</v>
       </c>
       <c r="G45">
-        <v>0.4561066226787983</v>
+        <v>0.45610662267879831</v>
       </c>
       <c r="H45">
-        <v>0.4661900489099834</v>
+        <v>0.46619004890998339</v>
       </c>
       <c r="I45">
-        <v>0.4774433768918624</v>
+        <v>0.47744337689186239</v>
       </c>
       <c r="J45">
-        <v>0.467732358376841</v>
+        <v>0.46773235837684102</v>
       </c>
       <c r="K45">
-        <v>0.4028607543951248</v>
+        <v>0.40286075439512481</v>
       </c>
       <c r="L45">
         <v>0.3462800028009313</v>
       </c>
       <c r="M45">
-        <v>0.3190159920785519</v>
+        <v>0.31901599207855191</v>
       </c>
       <c r="N45">
         <v>0.2814287147853537</v>
       </c>
       <c r="O45">
-        <v>0.2616885507415193</v>
+        <v>0.26168855074151931</v>
       </c>
       <c r="P45">
-        <v>0.281995735721865</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.28199573572186498</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>60</v>
       </c>
       <c r="B46">
-        <v>0.4394668336527263</v>
+        <v>0.43946683365272632</v>
       </c>
       <c r="C46">
         <v>0.5591180027354673</v>
       </c>
       <c r="D46">
-        <v>0.5477636570843054</v>
+        <v>0.54776365708430541</v>
       </c>
       <c r="E46">
-        <v>0.5507621771851556</v>
+        <v>0.55076217718515563</v>
       </c>
       <c r="F46">
-        <v>0.5031969904124143</v>
+        <v>0.50319699041241428</v>
       </c>
       <c r="G46">
-        <v>0.5168041226881349</v>
+        <v>0.51680412268813491</v>
       </c>
       <c r="H46">
-        <v>0.5195423765607605</v>
+        <v>0.51954237656076052</v>
       </c>
       <c r="I46">
-        <v>0.4667315423545108</v>
+        <v>0.46673154235451081</v>
       </c>
       <c r="J46">
-        <v>0.3989565235985604</v>
+        <v>0.39895652359856038</v>
       </c>
       <c r="K46">
-        <v>0.3266888977459105</v>
+        <v>0.32668889774591048</v>
       </c>
       <c r="L46">
-        <v>0.3104797792852512</v>
+        <v>0.31047977928525122</v>
       </c>
       <c r="M46">
-        <v>0.3066227991407262</v>
+        <v>0.30662279914072621</v>
       </c>
       <c r="N46">
-        <v>0.2819165743370015</v>
+        <v>0.28191657433700151</v>
       </c>
       <c r="O46">
-        <v>0.2692070962555708</v>
+        <v>0.26920709625557082</v>
       </c>
       <c r="P46">
-        <v>0.2697839148350858</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-        </is>
+        <v>0.26978391483508579</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>61</v>
       </c>
       <c r="B47">
-        <v>0.5645003231546881</v>
+        <v>0.56450032315468812</v>
       </c>
       <c r="C47">
-        <v>0.555096206963001</v>
+        <v>0.55509620696300099</v>
       </c>
       <c r="D47">
-        <v>0.546446661715915</v>
+        <v>0.54644666171591505</v>
       </c>
       <c r="E47">
         <v>0.5289284461284165</v>
       </c>
       <c r="F47">
-        <v>0.4547868450150153</v>
+        <v>0.45478684501501532</v>
       </c>
       <c r="G47">
-        <v>0.4749608932965673</v>
+        <v>0.47496089329656732</v>
       </c>
       <c r="H47">
-        <v>0.4957825915862449</v>
+        <v>0.49578259158624488</v>
       </c>
       <c r="I47">
-        <v>0.521676228091406</v>
+        <v>0.52167622809140601</v>
       </c>
       <c r="J47">
-        <v>0.4696226259304844</v>
+        <v>0.46962262593048443</v>
       </c>
       <c r="K47">
-        <v>0.4726144115977294</v>
+        <v>0.47261441159772938</v>
       </c>
       <c r="L47">
-        <v>0.4361740169927953</v>
+        <v>0.43617401699279529</v>
       </c>
       <c r="M47">
-        <v>0.4260998054309714</v>
+        <v>0.42609980543097142</v>
       </c>
       <c r="N47">
-        <v>0.4320268300794332</v>
+        <v>0.43202683007943321</v>
       </c>
       <c r="O47">
         <v>0.4302550635381337</v>
       </c>
       <c r="P47">
-        <v>0.4335330018168689</v>
+        <v>0.43353300181686888</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:P47">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="top10" dxfId="0" priority="1" rank="10"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/ROSA_vitaSPEC/Results/test_pretraitements/total.carotenes/Resultats_total.carotenes_moy_ADJR2.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/total.carotenes/Resultats_total.carotenes_moy_ADJR2.xlsx
@@ -19,11 +19,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t>Pretraitement</t>
   </si>
   <si>
+    <t>LV0_ADJR2</t>
+  </si>
+  <si>
     <t>LV1_ADJR2</t>
   </si>
   <si>
@@ -133,18 +136,6 @@
   </si>
   <si>
     <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
   </si>
   <si>
     <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
@@ -236,7 +227,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -244,39 +235,52 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -576,15 +580,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P47"/>
+  <dimension ref="A1:Q43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="52.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="17" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -633,2310 +637,2239 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2">
-        <v>0.36144363118969391</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C2">
-        <v>0.53133166596055514</v>
+        <v>0.36386424583395349</v>
       </c>
       <c r="D2">
-        <v>0.56857612116400613</v>
+        <v>0.53369760385734877</v>
       </c>
       <c r="E2">
-        <v>0.60907605691427913</v>
-      </c>
-      <c r="F2">
-        <v>0.62229486688522773</v>
+        <v>0.56987018462419214</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0.60878986941521951</v>
       </c>
       <c r="G2">
-        <v>0.64334524676382954</v>
+        <v>0.61851681313111029</v>
       </c>
       <c r="H2">
-        <v>0.6506065391814585</v>
+        <v>0.64317229517329011</v>
       </c>
       <c r="I2">
-        <v>0.64031745257852135</v>
+        <v>0.65233124423471822</v>
       </c>
       <c r="J2">
-        <v>0.62620736966865331</v>
+        <v>0.64434212798590351</v>
       </c>
       <c r="K2">
-        <v>0.60783342656461437</v>
+        <v>0.6261713362380914</v>
       </c>
       <c r="L2">
-        <v>0.60368907825939278</v>
+        <v>0.60827766287820717</v>
       </c>
       <c r="M2">
-        <v>0.56690174335558263</v>
+        <v>0.6010442690556681</v>
       </c>
       <c r="N2">
-        <v>0.53216288544782619</v>
+        <v>0.56118719771407777</v>
       </c>
       <c r="O2">
-        <v>0.51825047042475147</v>
+        <v>0.53038730542947943</v>
       </c>
       <c r="P2">
-        <v>0.54009444661197281</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.52143801057373784</v>
+      </c>
+      <c r="Q2">
+        <v>0.54124549828746471</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3">
-        <v>0.44078958663160511</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C3">
-        <v>0.54713418365491051</v>
-      </c>
-      <c r="D3">
-        <v>0.5497565610723455</v>
+        <v>0.44276357328460308</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0.54943845538386127</v>
       </c>
       <c r="E3">
-        <v>0.55631982983186579</v>
+        <v>0.554089643838103</v>
       </c>
       <c r="F3">
-        <v>0.5425640380366944</v>
+        <v>0.55783108808129711</v>
       </c>
       <c r="G3">
-        <v>0.53829008068003514</v>
+        <v>0.54700180540736931</v>
       </c>
       <c r="H3">
-        <v>0.49428370199424498</v>
+        <v>0.54267726568567032</v>
       </c>
       <c r="I3">
-        <v>0.48271558371129192</v>
+        <v>0.50012991410487784</v>
       </c>
       <c r="J3">
-        <v>0.46742958620927072</v>
+        <v>0.48520359426816911</v>
       </c>
       <c r="K3">
-        <v>0.4737545515285877</v>
+        <v>0.46739790502600831</v>
       </c>
       <c r="L3">
-        <v>0.45310914615854692</v>
+        <v>0.46779042621054678</v>
       </c>
       <c r="M3">
-        <v>0.39488302039579187</v>
+        <v>0.44385268336747308</v>
       </c>
       <c r="N3">
-        <v>0.33183768835026312</v>
+        <v>0.38318455108245369</v>
       </c>
       <c r="O3">
-        <v>0.28758086580308229</v>
+        <v>0.31713802028528132</v>
       </c>
       <c r="P3">
-        <v>0.24363850058758271</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.26809871178204742</v>
+      </c>
+      <c r="Q3">
+        <v>0.22427551073527449</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4">
-        <v>0.38307753119902199</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C4">
-        <v>0.51607763156052067</v>
+        <v>0.38654951312307068</v>
       </c>
       <c r="D4">
-        <v>0.53076886665888823</v>
-      </c>
-      <c r="E4">
-        <v>0.53162565264732209</v>
+        <v>0.52032549564422748</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0.53741893465810342</v>
       </c>
       <c r="F4">
-        <v>0.54634398924456307</v>
+        <v>0.53687704664408931</v>
       </c>
       <c r="G4">
-        <v>0.57713847369112248</v>
+        <v>0.55136641089119554</v>
       </c>
       <c r="H4">
-        <v>0.60317421605597488</v>
+        <v>0.58231010699986263</v>
       </c>
       <c r="I4">
-        <v>0.57730419472918426</v>
+        <v>0.60832790353359634</v>
       </c>
       <c r="J4">
-        <v>0.56104022838858314</v>
+        <v>0.58307686861371766</v>
       </c>
       <c r="K4">
-        <v>0.50093361499429145</v>
+        <v>0.56774617209168021</v>
       </c>
       <c r="L4">
-        <v>0.48104187332375109</v>
+        <v>0.5044227663604931</v>
       </c>
       <c r="M4">
-        <v>0.49864635381276978</v>
+        <v>0.48632501798299499</v>
       </c>
       <c r="N4">
-        <v>0.502717359409661</v>
+        <v>0.50639196637345285</v>
       </c>
       <c r="O4">
-        <v>0.49513223117120653</v>
+        <v>0.50719002473602726</v>
       </c>
       <c r="P4">
-        <v>0.49828760162800212</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.49930344857205378</v>
+      </c>
+      <c r="Q4">
+        <v>0.50001970568659304</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5">
-        <v>0.53892190298601395</v>
-      </c>
-      <c r="C5">
-        <v>0.54152326683538599</v>
+        <v>-1.8778932657874229E-2</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0.54029463061478544</v>
       </c>
       <c r="D5">
-        <v>0.54370424313434573</v>
+        <v>0.54393172325430583</v>
       </c>
       <c r="E5">
-        <v>0.53431910400601801</v>
+        <v>0.54314484848916844</v>
       </c>
       <c r="F5">
-        <v>0.53019080838282029</v>
+        <v>0.53540074898251278</v>
       </c>
       <c r="G5">
-        <v>0.5337599823395186</v>
+        <v>0.53037633582358623</v>
       </c>
       <c r="H5">
-        <v>0.52954902221113054</v>
+        <v>0.53338121001428485</v>
       </c>
       <c r="I5">
-        <v>0.51948473118230654</v>
+        <v>0.52272066618855506</v>
       </c>
       <c r="J5">
-        <v>0.4973113771447033</v>
+        <v>0.51012314472128051</v>
       </c>
       <c r="K5">
-        <v>0.49006831570933679</v>
+        <v>0.4855795382362954</v>
       </c>
       <c r="L5">
-        <v>0.48140237611428899</v>
+        <v>0.47215754503292229</v>
       </c>
       <c r="M5">
-        <v>0.46878504833059048</v>
+        <v>0.46259993687210132</v>
       </c>
       <c r="N5">
-        <v>0.46612826772116611</v>
+        <v>0.44827969516890043</v>
       </c>
       <c r="O5">
-        <v>0.4512282293001838</v>
+        <v>0.4452811502360603</v>
       </c>
       <c r="P5">
-        <v>0.46411350786679478</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.43170127409057668</v>
+      </c>
+      <c r="Q5">
+        <v>0.44888462474566121</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6">
-        <v>0.540261238234097</v>
-      </c>
-      <c r="C6">
-        <v>0.5464788514943435</v>
+        <v>-1.8778932657874229E-2</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0.53795149101079409</v>
       </c>
       <c r="D6">
-        <v>0.55037862925049885</v>
+        <v>0.54536446075388922</v>
       </c>
       <c r="E6">
-        <v>0.53385921143007853</v>
+        <v>0.55055507583278007</v>
       </c>
       <c r="F6">
-        <v>0.55515085139319864</v>
+        <v>0.5353804865128502</v>
       </c>
       <c r="G6">
-        <v>0.52302844226138545</v>
+        <v>0.55433492171384724</v>
       </c>
       <c r="H6">
-        <v>0.52924736627140245</v>
+        <v>0.5228099974506597</v>
       </c>
       <c r="I6">
-        <v>0.50584523338388665</v>
+        <v>0.52997339605600802</v>
       </c>
       <c r="J6">
-        <v>0.50129983461639049</v>
+        <v>0.50498656823338173</v>
       </c>
       <c r="K6">
-        <v>0.48894483908103531</v>
+        <v>0.5021164379526768</v>
       </c>
       <c r="L6">
-        <v>0.45627180651132998</v>
+        <v>0.48854999076726752</v>
       </c>
       <c r="M6">
-        <v>0.4219744037498977</v>
+        <v>0.45411952925447657</v>
       </c>
       <c r="N6">
-        <v>0.39634080459443799</v>
+        <v>0.42672839011813468</v>
       </c>
       <c r="O6">
-        <v>0.39533121560697199</v>
+        <v>0.39714760259354048</v>
       </c>
       <c r="P6">
-        <v>0.42834438225096172</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.39951019221316397</v>
+      </c>
+      <c r="Q6">
+        <v>0.43421520061914798</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B7">
-        <v>0.38065379749717138</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C7">
-        <v>0.53018257793625867</v>
+        <v>0.3849486964055302</v>
       </c>
       <c r="D7">
-        <v>0.60778798107732523</v>
+        <v>0.53734099725402718</v>
       </c>
       <c r="E7">
-        <v>0.6493116816476785</v>
-      </c>
-      <c r="F7">
-        <v>0.66944077958837522</v>
+        <v>0.61163975476562238</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.65119407977921784</v>
       </c>
       <c r="G7">
-        <v>0.68213796941584126</v>
+        <v>0.66970703951685306</v>
       </c>
       <c r="H7">
-        <v>0.66558558112923039</v>
+        <v>0.68525081997255866</v>
       </c>
       <c r="I7">
-        <v>0.65452426974463129</v>
+        <v>0.66529846696271078</v>
       </c>
       <c r="J7">
-        <v>0.63953302748956831</v>
+        <v>0.65429371867595398</v>
       </c>
       <c r="K7">
-        <v>0.64104966291517629</v>
+        <v>0.64004481720419171</v>
       </c>
       <c r="L7">
-        <v>0.58361913721900782</v>
+        <v>0.63954309696171563</v>
       </c>
       <c r="M7">
-        <v>0.58486908880449717</v>
+        <v>0.58216371269848333</v>
       </c>
       <c r="N7">
-        <v>0.59949702401763605</v>
+        <v>0.58159267876138276</v>
       </c>
       <c r="O7">
-        <v>0.59786966053211732</v>
+        <v>0.59807801167114338</v>
       </c>
       <c r="P7">
-        <v>0.59741397258360995</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.59492807857547803</v>
+      </c>
+      <c r="Q7">
+        <v>0.59350103960549094</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B8">
-        <v>0.44018424768172132</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C8">
-        <v>0.51068952665589329</v>
+        <v>0.4401874036031832</v>
       </c>
       <c r="D8">
-        <v>0.5630750579269731</v>
-      </c>
-      <c r="E8">
-        <v>0.58396205329769213</v>
+        <v>0.51335932547142182</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0.56664046981749172</v>
       </c>
       <c r="F8">
-        <v>0.58749297728621563</v>
+        <v>0.58625148938455107</v>
       </c>
       <c r="G8">
-        <v>0.58255125501336968</v>
+        <v>0.58978356194284798</v>
       </c>
       <c r="H8">
-        <v>0.59558992447741832</v>
+        <v>0.5882903687866422</v>
       </c>
       <c r="I8">
-        <v>0.60326952756734842</v>
+        <v>0.59973585488331438</v>
       </c>
       <c r="J8">
-        <v>0.54448518408540159</v>
+        <v>0.60744616733097545</v>
       </c>
       <c r="K8">
-        <v>0.50884579459925505</v>
+        <v>0.55053472797974812</v>
       </c>
       <c r="L8">
-        <v>0.50509487110833495</v>
+        <v>0.51460369996389244</v>
       </c>
       <c r="M8">
-        <v>0.51715512972395772</v>
+        <v>0.51004453358509705</v>
       </c>
       <c r="N8">
-        <v>0.54234451949186102</v>
+        <v>0.52360473244431693</v>
       </c>
       <c r="O8">
-        <v>0.52253879529743308</v>
+        <v>0.54594352471876217</v>
       </c>
       <c r="P8">
-        <v>0.52667140771030596</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.52368411378585145</v>
+      </c>
+      <c r="Q8">
+        <v>0.52806987378209769</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9">
-        <v>0.44196055008097529</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C9">
-        <v>0.51200914127282182</v>
+        <v>0.44133268895805039</v>
       </c>
       <c r="D9">
-        <v>0.55889971559109353</v>
-      </c>
-      <c r="E9">
-        <v>0.57655164271275905</v>
+        <v>0.51099721220461991</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0.56024868263833416</v>
       </c>
       <c r="F9">
-        <v>0.58349137435274978</v>
+        <v>0.57982662139397978</v>
       </c>
       <c r="G9">
-        <v>0.57979938283587451</v>
+        <v>0.58479661717448661</v>
       </c>
       <c r="H9">
-        <v>0.5884408771888896</v>
+        <v>0.58085040363325935</v>
       </c>
       <c r="I9">
-        <v>0.59815239039364843</v>
+        <v>0.59257291860047046</v>
       </c>
       <c r="J9">
-        <v>0.56139828903610989</v>
+        <v>0.60277904908582403</v>
       </c>
       <c r="K9">
-        <v>0.52575443904711316</v>
+        <v>0.56721814868252285</v>
       </c>
       <c r="L9">
-        <v>0.50684842267345087</v>
+        <v>0.53983592273975667</v>
       </c>
       <c r="M9">
-        <v>0.52152934992575251</v>
+        <v>0.52327126157020087</v>
       </c>
       <c r="N9">
-        <v>0.55073614971471108</v>
+        <v>0.53873693147552948</v>
       </c>
       <c r="O9">
-        <v>0.53297432910169085</v>
+        <v>0.56546476200952689</v>
       </c>
       <c r="P9">
-        <v>0.53084185336005596</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.55025725236342793</v>
+      </c>
+      <c r="Q9">
+        <v>0.5426832515343234</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B10">
-        <v>0.44044909391303888</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C10">
-        <v>0.51185822492730348</v>
+        <v>0.44141270396720439</v>
       </c>
       <c r="D10">
-        <v>0.55903231714063129</v>
-      </c>
-      <c r="E10">
-        <v>0.57878679496304497</v>
+        <v>0.51183798373715905</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0.5616544670536846</v>
       </c>
       <c r="F10">
-        <v>0.58005837513335334</v>
+        <v>0.57942761356529404</v>
       </c>
       <c r="G10">
-        <v>0.57874813125320734</v>
+        <v>0.58120696035419606</v>
       </c>
       <c r="H10">
-        <v>0.58707563338830959</v>
+        <v>0.57869418275026063</v>
       </c>
       <c r="I10">
-        <v>0.59853139302600589</v>
+        <v>0.58665178676603646</v>
       </c>
       <c r="J10">
-        <v>0.56073816666274123</v>
+        <v>0.59807333013263142</v>
       </c>
       <c r="K10">
-        <v>0.53214721039369028</v>
+        <v>0.56298780730132714</v>
       </c>
       <c r="L10">
-        <v>0.51166730875023403</v>
+        <v>0.53279812227431156</v>
       </c>
       <c r="M10">
-        <v>0.52591947747909207</v>
+        <v>0.51267646694967872</v>
       </c>
       <c r="N10">
-        <v>0.55614574593086341</v>
+        <v>0.52742612004040978</v>
       </c>
       <c r="O10">
-        <v>0.55020954199907046</v>
+        <v>0.55854108036207495</v>
       </c>
       <c r="P10">
-        <v>0.54406703259484845</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.55133495405107069</v>
+      </c>
+      <c r="Q10">
+        <v>0.54743054894463217</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B11">
-        <v>0.44125161736963708</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C11">
-        <v>0.51076433330764248</v>
+        <v>0.43721731880715781</v>
       </c>
       <c r="D11">
-        <v>0.56054244721759661</v>
-      </c>
-      <c r="E11">
-        <v>0.57836911503413402</v>
+        <v>0.50743852670505463</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0.55566583228796707</v>
       </c>
       <c r="F11">
-        <v>0.58337862959073483</v>
+        <v>0.57411554168084566</v>
       </c>
       <c r="G11">
-        <v>0.57593831485950664</v>
+        <v>0.58066086561058428</v>
       </c>
       <c r="H11">
-        <v>0.58662449615162193</v>
+        <v>0.56963958190335684</v>
       </c>
       <c r="I11">
-        <v>0.59986553897853445</v>
+        <v>0.5824567682991274</v>
       </c>
       <c r="J11">
-        <v>0.56276242947059429</v>
+        <v>0.59209006189494962</v>
       </c>
       <c r="K11">
-        <v>0.53286178178951626</v>
+        <v>0.55529093602634061</v>
       </c>
       <c r="L11">
-        <v>0.51720631266408268</v>
+        <v>0.52625424615306926</v>
       </c>
       <c r="M11">
-        <v>0.53134312769026482</v>
+        <v>0.50457860386652686</v>
       </c>
       <c r="N11">
-        <v>0.55170927717220919</v>
+        <v>0.52158296356522782</v>
       </c>
       <c r="O11">
-        <v>0.53566330146225538</v>
+        <v>0.54513058248211321</v>
       </c>
       <c r="P11">
-        <v>0.54893415936335488</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.52763022631027789</v>
+      </c>
+      <c r="Q11">
+        <v>0.54116609929987147</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B12">
-        <v>0.55132717412910026</v>
-      </c>
-      <c r="C12">
-        <v>0.55940852476462077</v>
+        <v>-1.8778932657874229E-2</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0.54875490739138255</v>
       </c>
       <c r="D12">
-        <v>0.56443523424455244</v>
+        <v>0.55450754490028609</v>
       </c>
       <c r="E12">
-        <v>0.56783211955232171</v>
+        <v>0.56015397556014102</v>
       </c>
       <c r="F12">
-        <v>0.57753787016190139</v>
+        <v>0.56502986081824547</v>
       </c>
       <c r="G12">
-        <v>0.58155794560565321</v>
+        <v>0.57567320960653134</v>
       </c>
       <c r="H12">
-        <v>0.58052441361603258</v>
+        <v>0.57788722386281677</v>
       </c>
       <c r="I12">
-        <v>0.56953132624965608</v>
+        <v>0.57504281004105273</v>
       </c>
       <c r="J12">
-        <v>0.55612984356364081</v>
+        <v>0.56351586152763555</v>
       </c>
       <c r="K12">
-        <v>0.53636493809767205</v>
+        <v>0.54492030145409964</v>
       </c>
       <c r="L12">
-        <v>0.50727673010873064</v>
+        <v>0.52760966389845798</v>
       </c>
       <c r="M12">
-        <v>0.48035322190985602</v>
+        <v>0.49706704175001459</v>
       </c>
       <c r="N12">
-        <v>0.4695611329375261</v>
+        <v>0.46753868558145328</v>
       </c>
       <c r="O12">
-        <v>0.45354144827702753</v>
+        <v>0.46176601873031009</v>
       </c>
       <c r="P12">
-        <v>0.4427295121923342</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.44670351377443518</v>
+      </c>
+      <c r="Q12">
+        <v>0.43574211687293052</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B13">
-        <v>0.54869299918602144</v>
-      </c>
-      <c r="C13">
-        <v>0.56892304488012202</v>
+        <v>-1.8778932657874229E-2</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0.54732036816243834</v>
       </c>
       <c r="D13">
-        <v>0.58239936200832987</v>
+        <v>0.56570359203523302</v>
       </c>
       <c r="E13">
-        <v>0.58693212036680487</v>
+        <v>0.5747875588950786</v>
       </c>
       <c r="F13">
-        <v>0.57801276339482155</v>
+        <v>0.57734444805574181</v>
       </c>
       <c r="G13">
-        <v>0.57189712439638407</v>
+        <v>0.56873978194181751</v>
       </c>
       <c r="H13">
-        <v>0.56966149504506358</v>
+        <v>0.55998463738536908</v>
       </c>
       <c r="I13">
-        <v>0.55159709055333861</v>
+        <v>0.55941257841572734</v>
       </c>
       <c r="J13">
-        <v>0.54001504746993079</v>
+        <v>0.53884544572799009</v>
       </c>
       <c r="K13">
-        <v>0.5107695444838859</v>
+        <v>0.52263176426022639</v>
       </c>
       <c r="L13">
-        <v>0.49886933276555112</v>
+        <v>0.49071685853922831</v>
       </c>
       <c r="M13">
-        <v>0.4906980696922138</v>
+        <v>0.47870878964249608</v>
       </c>
       <c r="N13">
-        <v>0.4805763056372066</v>
+        <v>0.46867264020681931</v>
       </c>
       <c r="O13">
-        <v>0.46420914622350451</v>
+        <v>0.45152061709036723</v>
       </c>
       <c r="P13">
-        <v>0.43378594015064342</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.43933209471941309</v>
+      </c>
+      <c r="Q13">
+        <v>0.40794919519612982</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B14">
-        <v>0.38315494931378152</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C14">
-        <v>0.53267154201847644</v>
+        <v>0.38611096003638001</v>
       </c>
       <c r="D14">
-        <v>0.6081578359023232</v>
+        <v>0.5354057176578132</v>
       </c>
       <c r="E14">
-        <v>0.64973498595367241</v>
-      </c>
-      <c r="F14">
-        <v>0.66786260331001268</v>
+        <v>0.61143989792992137</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0.65262977599848704</v>
       </c>
       <c r="G14">
-        <v>0.6792359727541557</v>
+        <v>0.67006564125723156</v>
       </c>
       <c r="H14">
-        <v>0.66480831167610721</v>
+        <v>0.68018123920640061</v>
       </c>
       <c r="I14">
-        <v>0.6560612022626332</v>
+        <v>0.6668672402522563</v>
       </c>
       <c r="J14">
-        <v>0.64349525068385638</v>
+        <v>0.65362707090680372</v>
       </c>
       <c r="K14">
-        <v>0.64308020130012955</v>
+        <v>0.64359691098458782</v>
       </c>
       <c r="L14">
-        <v>0.5831585284173274</v>
+        <v>0.64054299557793815</v>
       </c>
       <c r="M14">
-        <v>0.56692361028446725</v>
+        <v>0.58140651999706927</v>
       </c>
       <c r="N14">
-        <v>0.57682501101392591</v>
+        <v>0.56448232155870925</v>
       </c>
       <c r="O14">
-        <v>0.57978162926243981</v>
+        <v>0.57188752130054343</v>
       </c>
       <c r="P14">
-        <v>0.59728383339362334</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.57452330662388063</v>
+      </c>
+      <c r="Q14">
+        <v>0.58839166925301001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B15">
-        <v>0.38143682704367432</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C15">
-        <v>0.53042563363526241</v>
+        <v>0.38253676319933272</v>
       </c>
       <c r="D15">
-        <v>0.60793185651188941</v>
-      </c>
-      <c r="E15">
-        <v>0.65091355022389552</v>
+        <v>0.53193806378980413</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0.61294813786394231</v>
       </c>
       <c r="F15">
-        <v>0.66842856366242753</v>
+        <v>0.65205748863757274</v>
       </c>
       <c r="G15">
-        <v>0.67918389738128226</v>
+        <v>0.66974344117175932</v>
       </c>
       <c r="H15">
-        <v>0.66535010093037505</v>
+        <v>0.68117304517475041</v>
       </c>
       <c r="I15">
-        <v>0.65573604469702163</v>
+        <v>0.6669155061623685</v>
       </c>
       <c r="J15">
-        <v>0.64345548291621479</v>
+        <v>0.65880867197268189</v>
       </c>
       <c r="K15">
-        <v>0.64268788605045613</v>
+        <v>0.6485258228966353</v>
       </c>
       <c r="L15">
-        <v>0.58589195690289719</v>
+        <v>0.64681911423092187</v>
       </c>
       <c r="M15">
-        <v>0.56783322212185028</v>
+        <v>0.59209015878945148</v>
       </c>
       <c r="N15">
-        <v>0.57236865026848638</v>
+        <v>0.57265810978930098</v>
       </c>
       <c r="O15">
-        <v>0.57378197188970703</v>
+        <v>0.57880544681836255</v>
       </c>
       <c r="P15">
-        <v>0.59187035592130011</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.58089372347829238</v>
+      </c>
+      <c r="Q15">
+        <v>0.59858072554381636</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B16">
-        <v>0.38354978287820479</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C16">
-        <v>0.53414875529318306</v>
+        <v>0.3862281698813701</v>
       </c>
       <c r="D16">
-        <v>0.61411929278008459</v>
+        <v>0.53609889422114221</v>
       </c>
       <c r="E16">
-        <v>0.65226631815930769</v>
-      </c>
-      <c r="F16">
-        <v>0.67097567619313747</v>
+        <v>0.61356614667209664</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.65304938750975294</v>
       </c>
       <c r="G16">
-        <v>0.6808441646382879</v>
+        <v>0.67155095582495661</v>
       </c>
       <c r="H16">
-        <v>0.66711186419205049</v>
+        <v>0.68292583743903612</v>
       </c>
       <c r="I16">
-        <v>0.65813708059286458</v>
+        <v>0.66822061211665573</v>
       </c>
       <c r="J16">
-        <v>0.64564402323191017</v>
+        <v>0.66182472304910811</v>
       </c>
       <c r="K16">
-        <v>0.64398474619108614</v>
+        <v>0.64818056677652702</v>
       </c>
       <c r="L16">
-        <v>0.58865264974933351</v>
+        <v>0.64713083300276963</v>
       </c>
       <c r="M16">
-        <v>0.57342267498316213</v>
+        <v>0.59404778800707403</v>
       </c>
       <c r="N16">
-        <v>0.57652302457273263</v>
+        <v>0.57895008523702141</v>
       </c>
       <c r="O16">
-        <v>0.57603791106206226</v>
+        <v>0.58106940770771631</v>
       </c>
       <c r="P16">
-        <v>0.58977821353139848</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.58227611476272834</v>
+      </c>
+      <c r="Q16">
+        <v>0.59666111288815504</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B17">
-        <v>0.38478150679431983</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C17">
-        <v>0.53382331347093803</v>
+        <v>0.3856420531418025</v>
       </c>
       <c r="D17">
-        <v>0.61020054802475643</v>
+        <v>0.53603034829267149</v>
       </c>
       <c r="E17">
-        <v>0.64941097044721274</v>
-      </c>
-      <c r="F17">
-        <v>0.66650799136610928</v>
+        <v>0.61181510545879181</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.65228761069955121</v>
       </c>
       <c r="G17">
-        <v>0.67937919345278597</v>
+        <v>0.67164986504357893</v>
       </c>
       <c r="H17">
-        <v>0.66483893608464451</v>
+        <v>0.68302260899846767</v>
       </c>
       <c r="I17">
-        <v>0.65710434501090909</v>
+        <v>0.66942325276503667</v>
       </c>
       <c r="J17">
-        <v>0.64318087512419753</v>
+        <v>0.66114768665049561</v>
       </c>
       <c r="K17">
-        <v>0.64279231262483527</v>
+        <v>0.64920628907746158</v>
       </c>
       <c r="L17">
-        <v>0.58639614542124341</v>
+        <v>0.6491013152534294</v>
       </c>
       <c r="M17">
-        <v>0.56986600389292474</v>
+        <v>0.59578763779898736</v>
       </c>
       <c r="N17">
-        <v>0.57793498580070524</v>
+        <v>0.58316405690894291</v>
       </c>
       <c r="O17">
-        <v>0.58279404217406827</v>
+        <v>0.59060957351479837</v>
       </c>
       <c r="P17">
-        <v>0.5981478747412341</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.59548804987227244</v>
+      </c>
+      <c r="Q17">
+        <v>0.61057639704742683</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B18">
-        <v>0.5527824665139438</v>
-      </c>
-      <c r="C18">
-        <v>0.55941777152996597</v>
+        <v>-1.8778932657874229E-2</v>
+      </c>
+      <c r="C18" s="2">
+        <v>0.55276238802630351</v>
       </c>
       <c r="D18">
-        <v>0.56440030559621901</v>
+        <v>0.55866919338091103</v>
       </c>
       <c r="E18">
-        <v>0.5673516945961472</v>
+        <v>0.56308491554364848</v>
       </c>
       <c r="F18">
-        <v>0.58958975699372496</v>
+        <v>0.56540567648166107</v>
       </c>
       <c r="G18">
-        <v>0.58144165622942312</v>
+        <v>0.59150609358962003</v>
       </c>
       <c r="H18">
-        <v>0.59064254133931393</v>
+        <v>0.58050701503749658</v>
       </c>
       <c r="I18">
-        <v>0.58126258738133185</v>
+        <v>0.59223625710853456</v>
       </c>
       <c r="J18">
-        <v>0.58470657444823004</v>
+        <v>0.58407450987972021</v>
       </c>
       <c r="K18">
-        <v>0.58143445429729823</v>
+        <v>0.58335497896777277</v>
       </c>
       <c r="L18">
-        <v>0.57902576298129993</v>
+        <v>0.57792744364991644</v>
       </c>
       <c r="M18">
-        <v>0.56892558022655793</v>
+        <v>0.57870329687306654</v>
       </c>
       <c r="N18">
-        <v>0.56727112963534909</v>
+        <v>0.56658607230778357</v>
       </c>
       <c r="O18">
-        <v>0.54815812679781406</v>
+        <v>0.56532223441376883</v>
       </c>
       <c r="P18">
-        <v>0.54931818932363985</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.54762086303735502</v>
+      </c>
+      <c r="Q18">
+        <v>0.55349384300197035</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19">
-        <v>0.55371706770435358</v>
-      </c>
-      <c r="C19">
-        <v>0.5642447750806886</v>
+        <v>-1.8778932657874229E-2</v>
+      </c>
+      <c r="C19" s="2">
+        <v>0.55507286295944702</v>
       </c>
       <c r="D19">
-        <v>0.57069333799667266</v>
+        <v>0.56410170805061433</v>
       </c>
       <c r="E19">
-        <v>0.56202248602943861</v>
+        <v>0.57032521656487845</v>
       </c>
       <c r="F19">
-        <v>0.58884658457039796</v>
+        <v>0.56263262185269103</v>
       </c>
       <c r="G19">
-        <v>0.57771539392923854</v>
+        <v>0.58972626090469793</v>
       </c>
       <c r="H19">
-        <v>0.5873148705445006</v>
+        <v>0.57769470297414027</v>
       </c>
       <c r="I19">
-        <v>0.58833577778727475</v>
+        <v>0.58401191530047547</v>
       </c>
       <c r="J19">
-        <v>0.58376892239423206</v>
+        <v>0.57646913807799205</v>
       </c>
       <c r="K19">
-        <v>0.59639817750406665</v>
+        <v>0.57403133533682282</v>
       </c>
       <c r="L19">
-        <v>0.57071871233791582</v>
+        <v>0.58691863609299022</v>
       </c>
       <c r="M19">
-        <v>0.55785089556566991</v>
+        <v>0.55873447183886105</v>
       </c>
       <c r="N19">
-        <v>0.5491591721006811</v>
+        <v>0.54848616769496439</v>
       </c>
       <c r="O19">
-        <v>0.54589646320606422</v>
+        <v>0.54673247781620316</v>
       </c>
       <c r="P19">
-        <v>0.55169120983324915</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.5424781505511953</v>
+      </c>
+      <c r="Q19">
+        <v>0.5518460705024204</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B20">
-        <v>0.55496460165363115</v>
-      </c>
-      <c r="C20">
-        <v>0.56671395108200451</v>
+        <v>-1.8778932657874229E-2</v>
+      </c>
+      <c r="C20" s="2">
+        <v>0.55418998509697093</v>
       </c>
       <c r="D20">
-        <v>0.58140281137937089</v>
+        <v>0.56579082096988897</v>
       </c>
       <c r="E20">
-        <v>0.56808331551344082</v>
+        <v>0.58089251354165583</v>
       </c>
       <c r="F20">
-        <v>0.57795592498584336</v>
+        <v>0.56774346768979556</v>
       </c>
       <c r="G20">
-        <v>0.59607801421322837</v>
+        <v>0.57617659660877707</v>
       </c>
       <c r="H20">
-        <v>0.6009754247549246</v>
+        <v>0.59600516656015079</v>
       </c>
       <c r="I20">
-        <v>0.59975278117700881</v>
+        <v>0.59944412988200169</v>
       </c>
       <c r="J20">
-        <v>0.59782862937592773</v>
+        <v>0.59584301834357967</v>
       </c>
       <c r="K20">
-        <v>0.59586608976152877</v>
+        <v>0.59321419657314534</v>
       </c>
       <c r="L20">
-        <v>0.58013885284882882</v>
+        <v>0.59161804647901373</v>
       </c>
       <c r="M20">
-        <v>0.55709993109847122</v>
+        <v>0.57525848188092044</v>
       </c>
       <c r="N20">
-        <v>0.54743852449523134</v>
+        <v>0.55361230643839066</v>
       </c>
       <c r="O20">
-        <v>0.56956008177188922</v>
+        <v>0.54998858081105206</v>
       </c>
       <c r="P20">
-        <v>0.57017871056360014</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.57714041253860715</v>
+      </c>
+      <c r="Q20">
+        <v>0.57672192459500227</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B21">
-        <v>0.44243057735277719</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C21">
-        <v>0.54604336319428037</v>
-      </c>
-      <c r="D21">
-        <v>0.5516717297466005</v>
+        <v>0.44285120610387602</v>
+      </c>
+      <c r="D21" s="2">
+        <v>0.54739673180760184</v>
       </c>
       <c r="E21">
-        <v>0.5637977967205231</v>
+        <v>0.5551130950249713</v>
       </c>
       <c r="F21">
-        <v>0.56045227431069278</v>
+        <v>0.56781024179610773</v>
       </c>
       <c r="G21">
-        <v>0.54674885710750132</v>
+        <v>0.56655866887659689</v>
       </c>
       <c r="H21">
-        <v>0.48370657674198819</v>
+        <v>0.55694236718702406</v>
       </c>
       <c r="I21">
-        <v>0.46472289789562582</v>
+        <v>0.49833532954246013</v>
       </c>
       <c r="J21">
-        <v>0.46509989197131768</v>
+        <v>0.48166767052807341</v>
       </c>
       <c r="K21">
-        <v>0.44150343968285988</v>
+        <v>0.47106907577749818</v>
       </c>
       <c r="L21">
-        <v>0.41505294054502218</v>
+        <v>0.4515953649598769</v>
       </c>
       <c r="M21">
-        <v>0.37929682224810041</v>
+        <v>0.4225619304146695</v>
       </c>
       <c r="N21">
-        <v>0.33901367172539582</v>
+        <v>0.38731756113364751</v>
       </c>
       <c r="O21">
-        <v>0.28813551227270651</v>
+        <v>0.34812076417248272</v>
       </c>
       <c r="P21">
-        <v>0.22471491438369801</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.29809612728112561</v>
+      </c>
+      <c r="Q21">
+        <v>0.23683726170613731</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B22">
-        <v>0.44047925829184348</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C22">
-        <v>0.54434488967847872</v>
-      </c>
-      <c r="D22">
-        <v>0.55121677778640688</v>
+        <v>0.44281384784344152</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0.54550704985454479</v>
       </c>
       <c r="E22">
-        <v>0.56424416026266166</v>
+        <v>0.55034831264689132</v>
       </c>
       <c r="F22">
-        <v>0.56659591408193122</v>
+        <v>0.56452377470386494</v>
       </c>
       <c r="G22">
-        <v>0.5692388272138531</v>
+        <v>0.56264948181242691</v>
       </c>
       <c r="H22">
-        <v>0.50727910512235841</v>
+        <v>0.56587310303896898</v>
       </c>
       <c r="I22">
-        <v>0.47631012517293481</v>
+        <v>0.50359483914176728</v>
       </c>
       <c r="J22">
-        <v>0.48028817227324638</v>
+        <v>0.47575562638534591</v>
       </c>
       <c r="K22">
-        <v>0.46131141543894427</v>
+        <v>0.47734453435141377</v>
       </c>
       <c r="L22">
-        <v>0.43135274551294872</v>
+        <v>0.46264539918914838</v>
       </c>
       <c r="M22">
-        <v>0.3942772940030449</v>
+        <v>0.42918667214638279</v>
       </c>
       <c r="N22">
-        <v>0.36234564657247609</v>
+        <v>0.39083792498977271</v>
       </c>
       <c r="O22">
-        <v>0.31451866494382708</v>
+        <v>0.35693747331487202</v>
       </c>
       <c r="P22">
-        <v>0.26528609076109838</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.30440223683233281</v>
+      </c>
+      <c r="Q22">
+        <v>0.25218020501060873</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B23">
-        <v>0.54957816509814283</v>
-      </c>
-      <c r="C23">
-        <v>0.5319445768901544</v>
+        <v>-1.8778932657874229E-2</v>
+      </c>
+      <c r="C23" s="2">
+        <v>0.54928992177113578</v>
       </c>
       <c r="D23">
-        <v>0.54759104473372888</v>
+        <v>0.52900050379921537</v>
       </c>
       <c r="E23">
-        <v>0.56140984663032345</v>
+        <v>0.54853905690928417</v>
       </c>
       <c r="F23">
-        <v>0.5183878003490684</v>
+        <v>0.564059921181428</v>
       </c>
       <c r="G23">
-        <v>0.45005059779805801</v>
+        <v>0.52207203560197846</v>
       </c>
       <c r="H23">
-        <v>0.38739462456671209</v>
+        <v>0.45541274677984878</v>
       </c>
       <c r="I23">
-        <v>0.38191486414361858</v>
+        <v>0.39211636568168079</v>
       </c>
       <c r="J23">
-        <v>0.33712523502894781</v>
+        <v>0.38538794803126358</v>
       </c>
       <c r="K23">
-        <v>0.31090986173706903</v>
+        <v>0.34503714111779782</v>
       </c>
       <c r="L23">
-        <v>0.26518239774530861</v>
+        <v>0.31761881832101818</v>
       </c>
       <c r="M23">
-        <v>0.24759391091446081</v>
+        <v>0.2709731154264991</v>
       </c>
       <c r="N23">
-        <v>0.19813330070383131</v>
+        <v>0.25276391428964828</v>
       </c>
       <c r="O23">
-        <v>0.15981612399092279</v>
+        <v>0.2031052145599001</v>
       </c>
       <c r="P23">
-        <v>0.1058889274038084</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.16184605115443099</v>
+      </c>
+      <c r="Q23">
+        <v>0.10409737029445</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B24">
-        <v>9.9622684941437528E-2</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C24">
-        <v>4.4051334506747697E-2</v>
-      </c>
-      <c r="D24">
-        <v>6.8991414978740645E-2</v>
+        <v>0.57194814728902887</v>
+      </c>
+      <c r="D24" s="2">
+        <v>0.6324073217320747</v>
       </c>
       <c r="E24">
-        <v>-2.2438167904758121E-2</v>
+        <v>0.66570432404982927</v>
       </c>
       <c r="F24">
-        <v>-0.31725164742365147</v>
+        <v>0.68711593817328009</v>
       </c>
       <c r="G24">
-        <v>-0.20002537068957649</v>
+        <v>0.66683753878715235</v>
       </c>
       <c r="H24">
-        <v>-0.25924804983172478</v>
+        <v>0.66352208535549606</v>
       </c>
       <c r="I24">
-        <v>-0.31851934390167103</v>
+        <v>0.65950582543060099</v>
       </c>
       <c r="J24">
-        <v>-0.39491433244791352</v>
+        <v>0.64377360006021567</v>
       </c>
       <c r="K24">
-        <v>-0.43683022990335829</v>
+        <v>0.66517014709045386</v>
       </c>
       <c r="L24">
-        <v>-0.48054368699476369</v>
+        <v>0.67285626185225433</v>
       </c>
       <c r="M24">
-        <v>-0.46846107495118711</v>
+        <v>0.65561085846120326</v>
       </c>
       <c r="N24">
-        <v>-0.46294560092422188</v>
+        <v>0.62885286952143982</v>
       </c>
       <c r="O24">
-        <v>-0.4852012993549622</v>
+        <v>0.5997430861298495</v>
       </c>
       <c r="P24">
-        <v>-0.50436374746667167</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.5778042046609716</v>
+      </c>
+      <c r="Q24">
+        <v>0.54503820654503987</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B25">
-        <v>7.5660724008750874E-2</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C25">
-        <v>3.5867519559869568E-2</v>
+        <v>0.56900858907441798</v>
       </c>
       <c r="D25">
-        <v>-7.7191201385579556E-4</v>
+        <v>0.63322978365190163</v>
       </c>
       <c r="E25">
-        <v>-8.447490910147587E-2</v>
-      </c>
-      <c r="F25">
-        <v>-0.1533089672195472</v>
+        <v>0.67690087476881344</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0.70877114154302456</v>
       </c>
       <c r="G25">
-        <v>-0.29917805550635163</v>
+        <v>0.70241629806471095</v>
       </c>
       <c r="H25">
-        <v>-0.4171656826827827</v>
+        <v>0.71330502037668075</v>
       </c>
       <c r="I25">
-        <v>-0.50551222542204388</v>
+        <v>0.70650261055843111</v>
       </c>
       <c r="J25">
-        <v>-0.54298700299698799</v>
+        <v>0.69199676989173908</v>
       </c>
       <c r="K25">
-        <v>-0.55641412264453871</v>
+        <v>0.73076154883288091</v>
       </c>
       <c r="L25">
-        <v>-0.63546752126288719</v>
+        <v>0.73162481219400177</v>
       </c>
       <c r="M25">
-        <v>-0.71357709593669549</v>
+        <v>0.73284669008186165</v>
       </c>
       <c r="N25">
-        <v>-0.77480618401323376</v>
+        <v>0.71385649181701005</v>
       </c>
       <c r="O25">
-        <v>-0.8033320931835588</v>
+        <v>0.69929903498796142</v>
       </c>
       <c r="P25">
-        <v>-0.82793954894402222</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.67721206531180056</v>
+      </c>
+      <c r="Q25">
+        <v>0.64939833420787929</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B26">
-        <v>8.2453799252427629E-2</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C26">
-        <v>4.9673935038788662E-2</v>
+        <v>0.58800604017700908</v>
       </c>
       <c r="D26">
-        <v>5.3900744531080458E-2</v>
-      </c>
-      <c r="E26">
-        <v>-1.2462504947282141E-2</v>
+        <v>0.62024141703227331</v>
+      </c>
+      <c r="E26" s="2">
+        <v>0.65503369015766288</v>
       </c>
       <c r="F26">
-        <v>-0.1084617775083942</v>
+        <v>0.68657318786609356</v>
       </c>
       <c r="G26">
-        <v>-0.12848997450297339</v>
+        <v>0.66729595679681142</v>
       </c>
       <c r="H26">
-        <v>-0.2055737381541094</v>
+        <v>0.68345347264902356</v>
       </c>
       <c r="I26">
-        <v>-0.18658491558843879</v>
+        <v>0.68607589105137623</v>
       </c>
       <c r="J26">
-        <v>-0.12716374260296009</v>
+        <v>0.68134396568293953</v>
       </c>
       <c r="K26">
-        <v>-7.2242249762460228E-2</v>
+        <v>0.68130271796045916</v>
       </c>
       <c r="L26">
-        <v>-0.2301436280648278</v>
+        <v>0.69491350184040501</v>
       </c>
       <c r="M26">
-        <v>-0.3720972429703267</v>
+        <v>0.68608007079821853</v>
       </c>
       <c r="N26">
-        <v>-0.32262731175107262</v>
+        <v>0.68185582084368124</v>
       </c>
       <c r="O26">
-        <v>-0.3466396274595987</v>
+        <v>0.65969592234282681</v>
       </c>
       <c r="P26">
-        <v>-0.35638049166789498</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.63238211042524972</v>
+      </c>
+      <c r="Q26">
+        <v>0.60164765008756671</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B27">
-        <v>6.6935387395444718E-2</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C27">
-        <v>5.1415856817176357E-2</v>
+        <v>0.58859581217767876</v>
       </c>
       <c r="D27">
-        <v>-5.2719899748483623E-2</v>
-      </c>
-      <c r="E27">
-        <v>-3.5191172304316343E-4</v>
+        <v>0.61960517511794633</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0.65590004547631864</v>
       </c>
       <c r="F27">
-        <v>-0.1132533091966057</v>
+        <v>0.68329004775533553</v>
       </c>
       <c r="G27">
-        <v>-0.1065365921175368</v>
+        <v>0.66639316862423337</v>
       </c>
       <c r="H27">
-        <v>-4.1293375099463632E-2</v>
+        <v>0.68266610583365483</v>
       </c>
       <c r="I27">
-        <v>-3.4136832089805072E-2</v>
+        <v>0.67933991047566333</v>
       </c>
       <c r="J27">
-        <v>-0.1153147354859461</v>
+        <v>0.67495766973282323</v>
       </c>
       <c r="K27">
-        <v>-0.1989490500709036</v>
+        <v>0.66407865322215687</v>
       </c>
       <c r="L27">
-        <v>-0.26566049597654201</v>
+        <v>0.6677868643190249</v>
       </c>
       <c r="M27">
-        <v>-0.34535781141328392</v>
+        <v>0.66447433052289351</v>
       </c>
       <c r="N27">
-        <v>-0.27457800763875712</v>
+        <v>0.66117588279336625</v>
       </c>
       <c r="O27">
-        <v>-0.37678731851056579</v>
+        <v>0.64082608722136536</v>
       </c>
       <c r="P27">
-        <v>-0.42200497527479569</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.62503612728916047</v>
+      </c>
+      <c r="Q27">
+        <v>0.63191951181091865</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B28">
-        <v>0.57207174099497349</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C28">
-        <v>0.63357777566317541</v>
+        <v>0.57125023749114812</v>
       </c>
       <c r="D28">
-        <v>0.66599899365226578</v>
-      </c>
-      <c r="E28">
-        <v>0.68779123008811893</v>
+        <v>0.63689386437325235</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0.67933157964773783</v>
       </c>
       <c r="F28">
-        <v>0.66745485072092925</v>
+        <v>0.71009402213844164</v>
       </c>
       <c r="G28">
-        <v>0.66304344808407223</v>
+        <v>0.7029162490695654</v>
       </c>
       <c r="H28">
-        <v>0.66185877827421102</v>
+        <v>0.71194181838237114</v>
       </c>
       <c r="I28">
-        <v>0.64416399600098018</v>
+        <v>0.70597466398301567</v>
       </c>
       <c r="J28">
-        <v>0.66514433579143784</v>
+        <v>0.68255261884784613</v>
       </c>
       <c r="K28">
-        <v>0.67415527181794033</v>
+        <v>0.71367806932198263</v>
       </c>
       <c r="L28">
-        <v>0.66045338602619164</v>
+        <v>0.7217314229883266</v>
       </c>
       <c r="M28">
-        <v>0.63300412181955867</v>
+        <v>0.73053161366221442</v>
       </c>
       <c r="N28">
-        <v>0.60433042031549722</v>
+        <v>0.71883756002733512</v>
       </c>
       <c r="O28">
-        <v>0.58455132949499899</v>
+        <v>0.70972763212664436</v>
       </c>
       <c r="P28">
-        <v>0.54845491333551</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.69541087722337291</v>
+      </c>
+      <c r="Q28">
+        <v>0.65596750371371992</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B29">
-        <v>0.57276294060979249</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C29">
-        <v>0.63780054141778053</v>
+        <v>0.56884712624546496</v>
       </c>
       <c r="D29">
-        <v>0.6799487065455172</v>
+        <v>0.63231512145780633</v>
       </c>
       <c r="E29">
-        <v>0.71203016425872945</v>
-      </c>
-      <c r="F29">
-        <v>0.70412623559080734</v>
+        <v>0.67431969854651175</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.70677337463867507</v>
       </c>
       <c r="G29">
-        <v>0.71673223762092764</v>
+        <v>0.70104229458706913</v>
       </c>
       <c r="H29">
-        <v>0.7114679712218186</v>
+        <v>0.71122725409751553</v>
       </c>
       <c r="I29">
-        <v>0.69727293959763215</v>
+        <v>0.70622482567384881</v>
       </c>
       <c r="J29">
-        <v>0.73236772581139953</v>
+        <v>0.68253014400624756</v>
       </c>
       <c r="K29">
-        <v>0.7359475096495055</v>
+        <v>0.71306417674731304</v>
       </c>
       <c r="L29">
-        <v>0.73673191680872163</v>
+        <v>0.72179434362495887</v>
       </c>
       <c r="M29">
-        <v>0.71828388114330055</v>
+        <v>0.73068781606819355</v>
       </c>
       <c r="N29">
-        <v>0.70406279337022193</v>
+        <v>0.71757946444682175</v>
       </c>
       <c r="O29">
-        <v>0.68048981689224142</v>
+        <v>0.70621576585244705</v>
       </c>
       <c r="P29">
-        <v>0.65244641446021856</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.69353696885138505</v>
+      </c>
+      <c r="Q29">
+        <v>0.64943936601346663</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B30">
-        <v>0.58757566336085365</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C30">
-        <v>0.61963469857240883</v>
+        <v>0.57006591021041519</v>
       </c>
       <c r="D30">
-        <v>0.65427360143299074</v>
+        <v>0.63449413785693842</v>
       </c>
       <c r="E30">
-        <v>0.68363998992224684</v>
-      </c>
-      <c r="F30">
-        <v>0.66582822575549461</v>
+        <v>0.67726201313449108</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0.70809825578038521</v>
       </c>
       <c r="G30">
-        <v>0.68226746990866205</v>
+        <v>0.70307253089463084</v>
       </c>
       <c r="H30">
-        <v>0.67872139690265432</v>
+        <v>0.7092702708903823</v>
       </c>
       <c r="I30">
-        <v>0.67803284439443157</v>
+        <v>0.70682467664539361</v>
       </c>
       <c r="J30">
-        <v>0.67634442446475362</v>
+        <v>0.68374313127800534</v>
       </c>
       <c r="K30">
-        <v>0.68874875384178191</v>
+        <v>0.7135474037206111</v>
       </c>
       <c r="L30">
-        <v>0.68253931815286684</v>
+        <v>0.71991140645911555</v>
       </c>
       <c r="M30">
-        <v>0.6760503328270755</v>
+        <v>0.73130480205084059</v>
       </c>
       <c r="N30">
-        <v>0.65403361622891987</v>
+        <v>0.72021656203070084</v>
       </c>
       <c r="O30">
-        <v>0.62747942363625664</v>
+        <v>0.71012803230633614</v>
       </c>
       <c r="P30">
-        <v>0.59679404572519656</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.69432656497609258</v>
+      </c>
+      <c r="Q30">
+        <v>0.65326706283213098</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B31">
-        <v>0.59040194163942739</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C31">
-        <v>0.62221493050123677</v>
+        <v>0.56911562963045526</v>
       </c>
       <c r="D31">
-        <v>0.65721002906400783</v>
+        <v>0.63434713139018162</v>
       </c>
       <c r="E31">
-        <v>0.68583730066794768</v>
-      </c>
-      <c r="F31">
-        <v>0.66879941484414795</v>
+        <v>0.67679945186622092</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.70851536515788816</v>
       </c>
       <c r="G31">
-        <v>0.68361683749033708</v>
+        <v>0.69917088647007486</v>
       </c>
       <c r="H31">
-        <v>0.68006404784237673</v>
+        <v>0.70738315254206119</v>
       </c>
       <c r="I31">
-        <v>0.67516813353656868</v>
+        <v>0.70360886562974223</v>
       </c>
       <c r="J31">
-        <v>0.66657603917899089</v>
+        <v>0.6751566904989964</v>
       </c>
       <c r="K31">
-        <v>0.67127214444332928</v>
+        <v>0.70901308329263601</v>
       </c>
       <c r="L31">
-        <v>0.66859434066630052</v>
+        <v>0.71976852360298349</v>
       </c>
       <c r="M31">
-        <v>0.6661836604013287</v>
+        <v>0.73182824480097508</v>
       </c>
       <c r="N31">
-        <v>0.64791645203760995</v>
+        <v>0.71904334190723518</v>
       </c>
       <c r="O31">
-        <v>0.62890866658771549</v>
+        <v>0.70886562341266379</v>
       </c>
       <c r="P31">
-        <v>0.63635468349801416</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.70012908166255594</v>
+      </c>
+      <c r="Q31">
+        <v>0.66179230284755131</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B32">
-        <v>0.57172118500025504</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C32">
-        <v>0.63705723224415134</v>
+        <v>0.57107594803715589</v>
       </c>
       <c r="D32">
-        <v>0.67807316320917221</v>
-      </c>
-      <c r="E32">
-        <v>0.70910884506680938</v>
+        <v>0.6354372467415087</v>
+      </c>
+      <c r="E32" s="2">
+        <v>0.67773497481260858</v>
       </c>
       <c r="F32">
-        <v>0.70222766873253428</v>
+        <v>0.70988111930065334</v>
       </c>
       <c r="G32">
-        <v>0.71106565603461391</v>
+        <v>0.70147648700323972</v>
       </c>
       <c r="H32">
-        <v>0.7085478818112646</v>
+        <v>0.71244375582585762</v>
       </c>
       <c r="I32">
-        <v>0.68542226068234879</v>
+        <v>0.70553019230382463</v>
       </c>
       <c r="J32">
-        <v>0.71246816549311598</v>
+        <v>0.68310420391042614</v>
       </c>
       <c r="K32">
-        <v>0.72383341162863579</v>
+        <v>0.71381753981128171</v>
       </c>
       <c r="L32">
-        <v>0.73326307722405792</v>
+        <v>0.71920810919501543</v>
       </c>
       <c r="M32">
-        <v>0.72262360256943148</v>
+        <v>0.72314450533937424</v>
       </c>
       <c r="N32">
-        <v>0.71344283210854553</v>
+        <v>0.71046218625138102</v>
       </c>
       <c r="O32">
-        <v>0.70096701339363554</v>
+        <v>0.70307571842276906</v>
       </c>
       <c r="P32">
-        <v>0.66373954281380221</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.68947093847823493</v>
+      </c>
+      <c r="Q32">
+        <v>0.65807328379056007</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B33">
-        <v>0.56944684949880497</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C33">
-        <v>0.63418331728761079</v>
+        <v>0.57142949651451402</v>
       </c>
       <c r="D33">
-        <v>0.67760919660381502</v>
-      </c>
-      <c r="E33">
-        <v>0.70882413357174312</v>
+        <v>0.6355680277565452</v>
+      </c>
+      <c r="E33" s="2">
+        <v>0.67700355552896163</v>
       </c>
       <c r="F33">
-        <v>0.70439144594988135</v>
+        <v>0.70977832031151178</v>
       </c>
       <c r="G33">
-        <v>0.71326070299569677</v>
+        <v>0.70157374867818589</v>
       </c>
       <c r="H33">
-        <v>0.71066070651755386</v>
+        <v>0.71235636247580492</v>
       </c>
       <c r="I33">
-        <v>0.68780069966178525</v>
+        <v>0.70610265442016806</v>
       </c>
       <c r="J33">
-        <v>0.71585281366947517</v>
+        <v>0.6861218202541739</v>
       </c>
       <c r="K33">
-        <v>0.72561534280577211</v>
+        <v>0.71437423934548894</v>
       </c>
       <c r="L33">
-        <v>0.73226596836205649</v>
+        <v>0.72117570851850976</v>
       </c>
       <c r="M33">
-        <v>0.72035657591945601</v>
+        <v>0.72574031394613969</v>
       </c>
       <c r="N33">
-        <v>0.71181307906133962</v>
+        <v>0.71493504670581298</v>
       </c>
       <c r="O33">
-        <v>0.69427982166515423</v>
+        <v>0.70494717952363917</v>
       </c>
       <c r="P33">
-        <v>0.65098856028758045</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.69176979195244948</v>
+      </c>
+      <c r="Q33">
+        <v>0.65692463968115944</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B34">
-        <v>0.57119226654500055</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C34">
-        <v>0.63631570437678175</v>
+        <v>0.57163639967368063</v>
       </c>
       <c r="D34">
-        <v>0.67848940459507845</v>
+        <v>0.63677346688140357</v>
       </c>
       <c r="E34">
-        <v>0.71003455660887971</v>
-      </c>
-      <c r="F34">
-        <v>0.70323724474037463</v>
+        <v>0.67880567323652374</v>
+      </c>
+      <c r="F34" s="3">
+        <v>0.71023237137440232</v>
       </c>
       <c r="G34">
-        <v>0.71167107089074855</v>
+        <v>0.70271313540302371</v>
       </c>
       <c r="H34">
-        <v>0.70914008944073881</v>
+        <v>0.71449590632544246</v>
       </c>
       <c r="I34">
-        <v>0.68047199599250507</v>
+        <v>0.70891685273829841</v>
       </c>
       <c r="J34">
-        <v>0.71169727444307362</v>
+        <v>0.68947177836099949</v>
       </c>
       <c r="K34">
-        <v>0.72226678187232718</v>
+        <v>0.71519597499510412</v>
       </c>
       <c r="L34">
-        <v>0.73244944217319852</v>
+        <v>0.72310587574320428</v>
       </c>
       <c r="M34">
-        <v>0.72021621302927974</v>
+        <v>0.72769345935474239</v>
       </c>
       <c r="N34">
-        <v>0.71176206184464408</v>
+        <v>0.71648534436938027</v>
       </c>
       <c r="O34">
-        <v>0.69931096269499526</v>
+        <v>0.70645896457759194</v>
       </c>
       <c r="P34">
-        <v>0.65917735412469025</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.69268812591404694</v>
+      </c>
+      <c r="Q34">
+        <v>0.6578317653251583</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B35">
-        <v>0.56949039265180268</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C35">
-        <v>0.634932074197879</v>
+        <v>0.56909702708468346</v>
       </c>
       <c r="D35">
-        <v>0.67728395559348564</v>
-      </c>
-      <c r="E35">
-        <v>0.71020372719962199</v>
+        <v>0.63408643283734756</v>
+      </c>
+      <c r="E35" s="2">
+        <v>0.67765694276820165</v>
       </c>
       <c r="F35">
-        <v>0.70472579738964591</v>
+        <v>0.70941526895766172</v>
       </c>
       <c r="G35">
-        <v>0.71247299975384726</v>
+        <v>0.70171742447972529</v>
       </c>
       <c r="H35">
-        <v>0.70911799010064935</v>
+        <v>0.70954854938870127</v>
       </c>
       <c r="I35">
-        <v>0.68199540173207285</v>
+        <v>0.70609234271522647</v>
       </c>
       <c r="J35">
-        <v>0.71042916694800207</v>
+        <v>0.68517405763745998</v>
       </c>
       <c r="K35">
-        <v>0.72213896624703333</v>
+        <v>0.71461338364346316</v>
       </c>
       <c r="L35">
-        <v>0.73633938702755919</v>
+        <v>0.72011528333081309</v>
       </c>
       <c r="M35">
-        <v>0.72324246403311698</v>
+        <v>0.72840335517446286</v>
       </c>
       <c r="N35">
-        <v>0.71535418753119573</v>
+        <v>0.71593283487133719</v>
       </c>
       <c r="O35">
-        <v>0.70577123991625423</v>
+        <v>0.70971159838930387</v>
       </c>
       <c r="P35">
-        <v>0.67174265416192147</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.69504969196898025</v>
+      </c>
+      <c r="Q35">
+        <v>0.66032167161203525</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B36">
-        <v>0.57126823213314704</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C36">
-        <v>0.63638913489607818</v>
+        <v>0.57001370400866835</v>
       </c>
       <c r="D36">
-        <v>0.67995203796614367</v>
+        <v>0.63541805723302303</v>
       </c>
       <c r="E36">
-        <v>0.71100122328736459</v>
-      </c>
-      <c r="F36">
-        <v>0.70362075802679591</v>
+        <v>0.67667295468229394</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.70812687826900889</v>
       </c>
       <c r="G36">
-        <v>0.71418179504813828</v>
+        <v>0.6999597423888595</v>
       </c>
       <c r="H36">
-        <v>0.70830594886875531</v>
+        <v>0.7092710466050357</v>
       </c>
       <c r="I36">
-        <v>0.68514971101166111</v>
+        <v>0.70414122726262707</v>
       </c>
       <c r="J36">
-        <v>0.71449166583608537</v>
+        <v>0.67426849329642979</v>
       </c>
       <c r="K36">
-        <v>0.72311793741606789</v>
+        <v>0.70550472372281992</v>
       </c>
       <c r="L36">
-        <v>0.72546477674818877</v>
+        <v>0.71631129143188721</v>
       </c>
       <c r="M36">
-        <v>0.71250361841789922</v>
+        <v>0.73054219577777291</v>
       </c>
       <c r="N36">
-        <v>0.70310338629211466</v>
+        <v>0.71844070049616682</v>
       </c>
       <c r="O36">
-        <v>0.68980475493494875</v>
+        <v>0.71063332838084703</v>
       </c>
       <c r="P36">
-        <v>0.66006188510294084</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.70078928217215164</v>
+      </c>
+      <c r="Q36">
+        <v>0.65636249183764461</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B37">
-        <v>0.56808030906735674</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C37">
-        <v>0.63392221809804339</v>
-      </c>
-      <c r="D37">
-        <v>0.67663702531783099</v>
+        <v>0.59135824406612292</v>
+      </c>
+      <c r="D37" s="2">
+        <v>0.64837912743084092</v>
       </c>
       <c r="E37">
-        <v>0.70841949390752013</v>
+        <v>0.69863128526656748</v>
       </c>
       <c r="F37">
-        <v>0.70086604013958864</v>
+        <v>0.69509427438976723</v>
       </c>
       <c r="G37">
-        <v>0.70896170199600772</v>
+        <v>0.66272398360671037</v>
       </c>
       <c r="H37">
-        <v>0.70460245419283496</v>
+        <v>0.61112037618204063</v>
       </c>
       <c r="I37">
-        <v>0.68477202642191337</v>
+        <v>0.61948829535701577</v>
       </c>
       <c r="J37">
-        <v>0.71304082790638357</v>
+        <v>0.61125598252060787</v>
       </c>
       <c r="K37">
-        <v>0.71744079854136467</v>
+        <v>0.59041604650876545</v>
       </c>
       <c r="L37">
-        <v>0.7247470291691579</v>
+        <v>0.58881776231013938</v>
       </c>
       <c r="M37">
-        <v>0.71293190433570963</v>
+        <v>0.57711246541392325</v>
       </c>
       <c r="N37">
-        <v>0.70499298562123491</v>
+        <v>0.57895669219606749</v>
       </c>
       <c r="O37">
-        <v>0.69266522999461444</v>
+        <v>0.56189466081855488</v>
       </c>
       <c r="P37">
-        <v>0.65902005902575833</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.54618896866973921</v>
+      </c>
+      <c r="Q37">
+        <v>0.53814685419630437</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B38">
-        <v>0.57108489760247139</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C38">
-        <v>0.63606247420998374</v>
-      </c>
-      <c r="D38">
-        <v>0.67907877340682454</v>
+        <v>0.59275260532180352</v>
+      </c>
+      <c r="D38" s="2">
+        <v>0.65768635546992971</v>
       </c>
       <c r="E38">
-        <v>0.71070919818353773</v>
+        <v>0.70267794634006486</v>
       </c>
       <c r="F38">
-        <v>0.7046399167423022</v>
+        <v>0.70024894359835299</v>
       </c>
       <c r="G38">
-        <v>0.71487553567129902</v>
+        <v>0.66382497178268196</v>
       </c>
       <c r="H38">
-        <v>0.7083173703709601</v>
+        <v>0.62386168212155624</v>
       </c>
       <c r="I38">
-        <v>0.69007979842393385</v>
+        <v>0.65012427346143131</v>
       </c>
       <c r="J38">
-        <v>0.71647008203684648</v>
+        <v>0.64090099980783199</v>
       </c>
       <c r="K38">
-        <v>0.72411555787850634</v>
+        <v>0.64982488004286032</v>
       </c>
       <c r="L38">
-        <v>0.72984562644367057</v>
+        <v>0.67192677905113785</v>
       </c>
       <c r="M38">
-        <v>0.7204918999365878</v>
+        <v>0.66872899128145713</v>
       </c>
       <c r="N38">
-        <v>0.71053925130108686</v>
+        <v>0.66257825780276869</v>
       </c>
       <c r="O38">
-        <v>0.69736915549061607</v>
+        <v>0.66188255312474198</v>
       </c>
       <c r="P38">
-        <v>0.66195492048072291</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.64586124495459063</v>
+      </c>
+      <c r="Q38">
+        <v>0.61175706619432146</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B39">
-        <v>0.56980468208463853</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C39">
-        <v>0.63440129244068133</v>
-      </c>
-      <c r="D39">
-        <v>0.67611807364174747</v>
+        <v>0.59055679106902292</v>
+      </c>
+      <c r="D39" s="2">
+        <v>0.64993213344256451</v>
       </c>
       <c r="E39">
-        <v>0.70917563314594612</v>
+        <v>0.6990902342939721</v>
       </c>
       <c r="F39">
-        <v>0.70197238879206314</v>
+        <v>0.69524959993859436</v>
       </c>
       <c r="G39">
-        <v>0.71002198847339604</v>
+        <v>0.66017701186778011</v>
       </c>
       <c r="H39">
-        <v>0.70700308002135415</v>
+        <v>0.61695470647678341</v>
       </c>
       <c r="I39">
-        <v>0.68335118433764275</v>
+        <v>0.65060711798700721</v>
       </c>
       <c r="J39">
-        <v>0.71181530022708295</v>
+        <v>0.64368349041156658</v>
       </c>
       <c r="K39">
-        <v>0.72104418168822282</v>
+        <v>0.63903083728715815</v>
       </c>
       <c r="L39">
-        <v>0.72789084416119265</v>
+        <v>0.64551140309309507</v>
       </c>
       <c r="M39">
-        <v>0.71676853735709578</v>
+        <v>0.64611719398158907</v>
       </c>
       <c r="N39">
-        <v>0.70831553004892434</v>
+        <v>0.64034753277896339</v>
       </c>
       <c r="O39">
-        <v>0.69955580828440111</v>
+        <v>0.64362395186935273</v>
       </c>
       <c r="P39">
-        <v>0.66504190578838263</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.6393937353759046</v>
+      </c>
+      <c r="Q39">
+        <v>0.61055615594832502</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B40">
-        <v>0.56974485564427402</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C40">
-        <v>0.63612175982851937</v>
+        <v>0.55378467501422202</v>
       </c>
       <c r="D40">
-        <v>0.67969327830472581</v>
-      </c>
-      <c r="E40">
-        <v>0.71124450803471173</v>
+        <v>0.54929383091508122</v>
+      </c>
+      <c r="E40" s="2">
+        <v>0.58399416250258585</v>
       </c>
       <c r="F40">
-        <v>0.70642350539939869</v>
+        <v>0.64374310208263008</v>
       </c>
       <c r="G40">
-        <v>0.71425602964846013</v>
+        <v>0.64812004259635803</v>
       </c>
       <c r="H40">
-        <v>0.7096919180056086</v>
+        <v>0.65036291442486782</v>
       </c>
       <c r="I40">
-        <v>0.68463434105540188</v>
+        <v>0.62734982985712462</v>
       </c>
       <c r="J40">
-        <v>0.7141645397607751</v>
+        <v>0.62316595846347334</v>
       </c>
       <c r="K40">
-        <v>0.72264191038034109</v>
+        <v>0.60982753517145383</v>
       </c>
       <c r="L40">
-        <v>0.73554350978371297</v>
+        <v>0.58030742574491034</v>
       </c>
       <c r="M40">
-        <v>0.72264018572116462</v>
+        <v>0.54318766525142037</v>
       </c>
       <c r="N40">
-        <v>0.71368581276253928</v>
+        <v>0.50449183193039016</v>
       </c>
       <c r="O40">
-        <v>0.70263329860696644</v>
+        <v>0.4709528373095424</v>
       </c>
       <c r="P40">
-        <v>0.65874980186562038</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.43513772985756671</v>
+      </c>
+      <c r="Q40">
+        <v>0.38520601227100593</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B41">
-        <v>0.59129594155369314</v>
-      </c>
-      <c r="C41">
-        <v>0.64893213031715313</v>
+        <v>-1.8778932657874229E-2</v>
+      </c>
+      <c r="C41" s="2">
+        <v>0.53971361544363361</v>
       </c>
       <c r="D41">
-        <v>0.69733233923453652</v>
+        <v>0.58010755976944817</v>
       </c>
       <c r="E41">
-        <v>0.69254362208177001</v>
+        <v>0.56148062744821703</v>
       </c>
       <c r="F41">
-        <v>0.65812802364515877</v>
+        <v>0.52902096529799691</v>
       </c>
       <c r="G41">
-        <v>0.60343318831808024</v>
+        <v>0.47937167348101178</v>
       </c>
       <c r="H41">
-        <v>0.61167974902301014</v>
+        <v>0.45949164622389438</v>
       </c>
       <c r="I41">
-        <v>0.5993492403434717</v>
+        <v>0.46972158083856291</v>
       </c>
       <c r="J41">
-        <v>0.58204615751383892</v>
+        <v>0.48158141593964199</v>
       </c>
       <c r="K41">
-        <v>0.57950017978243373</v>
+        <v>0.47401623843881319</v>
       </c>
       <c r="L41">
-        <v>0.55971177456586241</v>
+        <v>0.41326731259911398</v>
       </c>
       <c r="M41">
-        <v>0.56126380938823817</v>
+        <v>0.35270408069480591</v>
       </c>
       <c r="N41">
-        <v>0.54584483517667437</v>
+        <v>0.32417385000817028</v>
       </c>
       <c r="O41">
-        <v>0.52780525963191771</v>
+        <v>0.28466364633085312</v>
       </c>
       <c r="P41">
-        <v>0.51730878351610154</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.25690976052669662</v>
+      </c>
+      <c r="Q41">
+        <v>0.27071571950981271</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B42">
-        <v>0.59252343342890634</v>
+        <v>-1.8778932657874229E-2</v>
       </c>
       <c r="C42">
-        <v>0.66079950545151911</v>
-      </c>
-      <c r="D42">
-        <v>0.707637900473716</v>
+        <v>0.43908893348699329</v>
+      </c>
+      <c r="D42" s="2">
+        <v>0.55838060374129084</v>
       </c>
       <c r="E42">
-        <v>0.70441878066859576</v>
+        <v>0.54963643515740146</v>
       </c>
       <c r="F42">
-        <v>0.66792975167987745</v>
+        <v>0.55057038552432758</v>
       </c>
       <c r="G42">
-        <v>0.62572575200032809</v>
+        <v>0.50685413720124917</v>
       </c>
       <c r="H42">
-        <v>0.65061557855567098</v>
+        <v>0.52083003915211878</v>
       </c>
       <c r="I42">
-        <v>0.64569281148776403</v>
+        <v>0.52235630665209198</v>
       </c>
       <c r="J42">
-        <v>0.64773055934778379</v>
+        <v>0.47142225756133072</v>
       </c>
       <c r="K42">
-        <v>0.66848748491786647</v>
+        <v>0.40716430228964617</v>
       </c>
       <c r="L42">
-        <v>0.66756676479960009</v>
+        <v>0.33820008420365322</v>
       </c>
       <c r="M42">
-        <v>0.65936598874923957</v>
+        <v>0.32036525226165352</v>
       </c>
       <c r="N42">
-        <v>0.6558427640331782</v>
+        <v>0.31619023357525922</v>
       </c>
       <c r="O42">
-        <v>0.63835859371324644</v>
+        <v>0.29111038876063011</v>
       </c>
       <c r="P42">
-        <v>0.60534241857516291</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.28135188882795847</v>
+      </c>
+      <c r="Q42">
+        <v>0.28653978172157291</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B43">
-        <v>0.59454127480355667</v>
-      </c>
-      <c r="C43">
-        <v>0.65842552214531058</v>
+        <v>-1.8778932657874229E-2</v>
+      </c>
+      <c r="C43" s="2">
+        <v>0.56353638369157866</v>
       </c>
       <c r="D43">
-        <v>0.70705912456906306</v>
+        <v>0.55427537675215699</v>
       </c>
       <c r="E43">
-        <v>0.70211781357300962</v>
+        <v>0.54228956366246828</v>
       </c>
       <c r="F43">
-        <v>0.67012487711422253</v>
+        <v>0.52319448466600282</v>
       </c>
       <c r="G43">
-        <v>0.62816271402519197</v>
+        <v>0.44674571853629091</v>
       </c>
       <c r="H43">
-        <v>0.65878634234934719</v>
+        <v>0.46995503590946769</v>
       </c>
       <c r="I43">
-        <v>0.65498910100562202</v>
+        <v>0.49034402467588178</v>
       </c>
       <c r="J43">
-        <v>0.65035796613476682</v>
+        <v>0.51352257698625625</v>
       </c>
       <c r="K43">
-        <v>0.65784930434429001</v>
+        <v>0.45631863683721191</v>
       </c>
       <c r="L43">
-        <v>0.65916959003293929</v>
+        <v>0.45819657824919852</v>
       </c>
       <c r="M43">
-        <v>0.65398580721723998</v>
+        <v>0.41753721883524852</v>
       </c>
       <c r="N43">
-        <v>0.65591200287369322</v>
+        <v>0.41118890896258009</v>
       </c>
       <c r="O43">
-        <v>0.64947412843294938</v>
+        <v>0.41931660088977862</v>
       </c>
       <c r="P43">
-        <v>0.62608641451983404</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>58</v>
-      </c>
-      <c r="B44">
-        <v>0.55167168348531403</v>
-      </c>
-      <c r="C44">
-        <v>0.54644565521480948</v>
-      </c>
-      <c r="D44">
-        <v>0.58410493727270385</v>
-      </c>
-      <c r="E44">
-        <v>0.64259075955866085</v>
-      </c>
-      <c r="F44">
-        <v>0.64332766778511175</v>
-      </c>
-      <c r="G44">
-        <v>0.64437993744090583</v>
-      </c>
-      <c r="H44">
-        <v>0.62078934683162024</v>
-      </c>
-      <c r="I44">
-        <v>0.61647976123596249</v>
-      </c>
-      <c r="J44">
-        <v>0.60598718918233008</v>
-      </c>
-      <c r="K44">
-        <v>0.57639951506939591</v>
-      </c>
-      <c r="L44">
-        <v>0.53550673441322649</v>
-      </c>
-      <c r="M44">
-        <v>0.498059574129741</v>
-      </c>
-      <c r="N44">
-        <v>0.46511111753931411</v>
-      </c>
-      <c r="O44">
-        <v>0.4310097701313374</v>
-      </c>
-      <c r="P44">
-        <v>0.38421830058250639</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>59</v>
-      </c>
-      <c r="B45">
-        <v>0.5386367630112614</v>
-      </c>
-      <c r="C45">
-        <v>0.57917926327205105</v>
-      </c>
-      <c r="D45">
-        <v>0.56001574548457989</v>
-      </c>
-      <c r="E45">
-        <v>0.52919103632801334</v>
-      </c>
-      <c r="F45">
-        <v>0.48030232328121131</v>
-      </c>
-      <c r="G45">
-        <v>0.45610662267879831</v>
-      </c>
-      <c r="H45">
-        <v>0.46619004890998339</v>
-      </c>
-      <c r="I45">
-        <v>0.47744337689186239</v>
-      </c>
-      <c r="J45">
-        <v>0.46773235837684102</v>
-      </c>
-      <c r="K45">
-        <v>0.40286075439512481</v>
-      </c>
-      <c r="L45">
-        <v>0.3462800028009313</v>
-      </c>
-      <c r="M45">
-        <v>0.31901599207855191</v>
-      </c>
-      <c r="N45">
-        <v>0.2814287147853537</v>
-      </c>
-      <c r="O45">
-        <v>0.26168855074151931</v>
-      </c>
-      <c r="P45">
-        <v>0.28199573572186498</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>60</v>
-      </c>
-      <c r="B46">
-        <v>0.43946683365272632</v>
-      </c>
-      <c r="C46">
-        <v>0.5591180027354673</v>
-      </c>
-      <c r="D46">
-        <v>0.54776365708430541</v>
-      </c>
-      <c r="E46">
-        <v>0.55076217718515563</v>
-      </c>
-      <c r="F46">
-        <v>0.50319699041241428</v>
-      </c>
-      <c r="G46">
-        <v>0.51680412268813491</v>
-      </c>
-      <c r="H46">
-        <v>0.51954237656076052</v>
-      </c>
-      <c r="I46">
-        <v>0.46673154235451081</v>
-      </c>
-      <c r="J46">
-        <v>0.39895652359856038</v>
-      </c>
-      <c r="K46">
-        <v>0.32668889774591048</v>
-      </c>
-      <c r="L46">
-        <v>0.31047977928525122</v>
-      </c>
-      <c r="M46">
-        <v>0.30662279914072621</v>
-      </c>
-      <c r="N46">
-        <v>0.28191657433700151</v>
-      </c>
-      <c r="O46">
-        <v>0.26920709625557082</v>
-      </c>
-      <c r="P46">
-        <v>0.26978391483508579</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>61</v>
-      </c>
-      <c r="B47">
-        <v>0.56450032315468812</v>
-      </c>
-      <c r="C47">
-        <v>0.55509620696300099</v>
-      </c>
-      <c r="D47">
-        <v>0.54644666171591505</v>
-      </c>
-      <c r="E47">
-        <v>0.5289284461284165</v>
-      </c>
-      <c r="F47">
-        <v>0.45478684501501532</v>
-      </c>
-      <c r="G47">
-        <v>0.47496089329656732</v>
-      </c>
-      <c r="H47">
-        <v>0.49578259158624488</v>
-      </c>
-      <c r="I47">
-        <v>0.52167622809140601</v>
-      </c>
-      <c r="J47">
-        <v>0.46962262593048443</v>
-      </c>
-      <c r="K47">
-        <v>0.47261441159772938</v>
-      </c>
-      <c r="L47">
-        <v>0.43617401699279529</v>
-      </c>
-      <c r="M47">
-        <v>0.42609980543097142</v>
-      </c>
-      <c r="N47">
-        <v>0.43202683007943321</v>
-      </c>
-      <c r="O47">
-        <v>0.4302550635381337</v>
-      </c>
-      <c r="P47">
-        <v>0.43353300181686888</v>
+        <v>0.41907343991621021</v>
+      </c>
+      <c r="Q43">
+        <v>0.42219451137434838</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:P47">
-    <cfRule type="colorScale" priority="2">
+  <conditionalFormatting sqref="B2:Q43">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2946,7 +2879,6 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="top10" dxfId="0" priority="1" rank="10"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
